--- a/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12625,7 +12625,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13936,7 +13936,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14446,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15041,7 +15041,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15296,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16008,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17161,7 +17161,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17416,7 +17416,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17501,7 +17501,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17586,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17671,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17841,7 +17841,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18100,7 +18100,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18367,7 +18367,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18812,7 +18812,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19326,7 +19326,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20176,7 +20176,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20261,7 +20261,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20686,7 +20686,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20941,7 +20941,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21026,7 +21026,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21281,7 +21281,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21536,7 +21536,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21706,7 +21706,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21795,7 +21795,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22062,7 +22062,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22151,7 +22151,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22240,7 +22240,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22507,7 +22507,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22596,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22685,7 +22685,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22774,7 +22774,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22952,7 +22952,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23041,7 +23041,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23130,7 +23130,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23308,7 +23308,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23397,7 +23397,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23486,7 +23486,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23575,7 +23575,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23753,7 +23753,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24198,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24287,7 +24287,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24376,7 +24376,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24461,7 +24461,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24716,7 +24716,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24886,7 +24886,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24971,7 +24971,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25056,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25226,7 +25226,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25396,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25566,7 +25566,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25736,7 +25736,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25906,7 +25906,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26076,7 +26076,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26161,7 +26161,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26335,7 +26335,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26424,7 +26424,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26602,7 +26602,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26780,7 +26780,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26869,7 +26869,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26958,7 +26958,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27225,7 +27225,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27403,7 +27403,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27492,7 +27492,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27670,7 +27670,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27759,7 +27759,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27848,7 +27848,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27937,7 +27937,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28026,7 +28026,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28196,7 +28196,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28281,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28366,7 +28366,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28451,7 +28451,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28876,7 +28876,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29046,7 +29046,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29216,7 +29216,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29301,7 +29301,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29386,7 +29386,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29471,7 +29471,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29556,7 +29556,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29641,7 +29641,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29726,7 +29726,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29811,7 +29811,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29985,7 +29985,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30341,7 +30341,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30430,7 +30430,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30608,7 +30608,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31231,7 +31231,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31498,7 +31498,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31587,7 +31587,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31676,7 +31676,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31761,7 +31761,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31846,7 +31846,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31931,7 +31931,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32101,7 +32101,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32186,7 +32186,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32271,7 +32271,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32356,7 +32356,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32441,7 +32441,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32526,7 +32526,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32611,7 +32611,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32696,7 +32696,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32951,7 +32951,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33036,7 +33036,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33291,7 +33291,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33376,7 +33376,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33461,7 +33461,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33724,7 +33724,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33813,7 +33813,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33902,7 +33902,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33991,7 +33991,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34080,7 +34080,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34169,7 +34169,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34258,7 +34258,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34347,7 +34347,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34436,7 +34436,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34525,7 +34525,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34614,7 +34614,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34703,7 +34703,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34881,7 +34881,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35148,7 +35148,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35237,7 +35237,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35326,7 +35326,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35411,7 +35411,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35496,7 +35496,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35581,7 +35581,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35836,7 +35836,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36006,7 +36006,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36091,7 +36091,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36176,7 +36176,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36261,7 +36261,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36350,7 +36350,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36439,7 +36439,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36706,7 +36706,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36795,7 +36795,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36884,7 +36884,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36973,7 +36973,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37062,7 +37062,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37151,7 +37151,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37236,7 +37236,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37321,7 +37321,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37491,7 +37491,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37576,7 +37576,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37661,7 +37661,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37746,7 +37746,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37831,7 +37831,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38001,7 +38001,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38086,7 +38086,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38256,7 +38256,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38341,7 +38341,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38426,7 +38426,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38511,7 +38511,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38596,7 +38596,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38681,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38766,7 +38766,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38851,7 +38851,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38936,7 +38936,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39021,7 +39021,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39110,7 +39110,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39199,7 +39199,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39288,7 +39288,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39377,7 +39377,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39466,7 +39466,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39644,7 +39644,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39822,7 +39822,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39911,7 +39911,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40000,7 +40000,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40089,7 +40089,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40178,7 +40178,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40267,7 +40267,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40445,7 +40445,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40534,7 +40534,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40623,7 +40623,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40712,7 +40712,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40886,7 +40886,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40971,7 +40971,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41141,7 +41141,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41226,7 +41226,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41311,7 +41311,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41396,7 +41396,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41481,7 +41481,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41566,7 +41566,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41651,7 +41651,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41736,7 +41736,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41825,7 +41825,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41914,7 +41914,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42003,7 +42003,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42092,7 +42092,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42181,7 +42181,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42270,7 +42270,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42359,7 +42359,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42448,7 +42448,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42537,7 +42537,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42626,7 +42626,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42711,7 +42711,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42796,7 +42796,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42881,7 +42881,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43051,7 +43051,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43221,7 +43221,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43306,7 +43306,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43391,7 +43391,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43476,7 +43476,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43561,7 +43561,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43646,7 +43646,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43731,7 +43731,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43816,7 +43816,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43901,7 +43901,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43986,7 +43986,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44071,7 +44071,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44156,7 +44156,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44241,7 +44241,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44411,7 +44411,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44496,7 +44496,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44585,7 +44585,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44674,7 +44674,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44763,7 +44763,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44852,7 +44852,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44941,7 +44941,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45030,7 +45030,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45119,7 +45119,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45208,7 +45208,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45297,7 +45297,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45386,7 +45386,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45475,7 +45475,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45564,7 +45564,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45653,7 +45653,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45742,7 +45742,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45831,7 +45831,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45920,7 +45920,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46009,7 +46009,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46098,7 +46098,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46187,7 +46187,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46276,7 +46276,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46361,7 +46361,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46446,7 +46446,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46531,7 +46531,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46616,7 +46616,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46701,7 +46701,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46786,7 +46786,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46871,7 +46871,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46956,7 +46956,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47041,7 +47041,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47126,7 +47126,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47211,7 +47211,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47300,7 +47300,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47389,7 +47389,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47478,7 +47478,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47567,7 +47567,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47656,7 +47656,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47745,7 +47745,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47834,7 +47834,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47923,7 +47923,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48012,7 +48012,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48101,7 +48101,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48186,7 +48186,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48271,7 +48271,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48356,7 +48356,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48441,7 +48441,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48526,7 +48526,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48696,7 +48696,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48781,7 +48781,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48866,7 +48866,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48951,7 +48951,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49036,7 +49036,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49125,7 +49125,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49214,7 +49214,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49303,7 +49303,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49392,7 +49392,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49481,7 +49481,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49570,7 +49570,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49659,7 +49659,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49748,7 +49748,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49837,7 +49837,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49926,7 +49926,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50011,7 +50011,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50096,7 +50096,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50181,7 +50181,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50266,7 +50266,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50436,7 +50436,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50521,7 +50521,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50606,7 +50606,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50691,7 +50691,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50776,7 +50776,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50861,7 +50861,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50946,7 +50946,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51031,7 +51031,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51116,7 +51116,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51201,7 +51201,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51286,7 +51286,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51371,7 +51371,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51456,7 +51456,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51541,7 +51541,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51626,7 +51626,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51711,7 +51711,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51796,7 +51796,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51885,7 +51885,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51974,7 +51974,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52063,7 +52063,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52152,7 +52152,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52241,7 +52241,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52330,7 +52330,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52419,7 +52419,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52508,7 +52508,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52597,7 +52597,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52686,7 +52686,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52775,7 +52775,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52864,7 +52864,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52953,7 +52953,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53042,7 +53042,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53131,7 +53131,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53220,7 +53220,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53309,7 +53309,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53398,7 +53398,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53487,7 +53487,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53576,7 +53576,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53661,7 +53661,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53746,7 +53746,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53831,7 +53831,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53916,7 +53916,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54001,7 +54001,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54086,7 +54086,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54171,7 +54171,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54256,7 +54256,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54426,7 +54426,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54511,7 +54511,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54596,7 +54596,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54681,7 +54681,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54766,7 +54766,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54851,7 +54851,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54936,7 +54936,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55021,7 +55021,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55106,7 +55106,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55191,7 +55191,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55276,7 +55276,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55361,7 +55361,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55446,7 +55446,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55531,7 +55531,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55616,7 +55616,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55701,7 +55701,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55786,7 +55786,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55871,7 +55871,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55956,7 +55956,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56041,7 +56041,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56126,7 +56126,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56211,7 +56211,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56296,7 +56296,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56381,7 +56381,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56466,7 +56466,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56551,7 +56551,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56636,7 +56636,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56721,7 +56721,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56806,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56891,7 +56891,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56976,7 +56976,7 @@
       </c>
       <c r="S655" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57061,7 +57061,7 @@
       </c>
       <c r="S656" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57146,7 +57146,7 @@
       </c>
       <c r="S657" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57231,7 +57231,7 @@
       </c>
       <c r="S658" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57316,7 +57316,7 @@
       </c>
       <c r="S659" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57401,7 +57401,7 @@
       </c>
       <c r="S660" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57486,7 +57486,7 @@
       </c>
       <c r="S661" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57571,7 +57571,7 @@
       </c>
       <c r="S662" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57656,7 +57656,7 @@
       </c>
       <c r="S663" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57741,7 +57741,7 @@
       </c>
       <c r="S664" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57826,7 +57826,7 @@
       </c>
       <c r="S665" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57911,7 +57911,7 @@
       </c>
       <c r="S666" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57996,7 +57996,7 @@
       </c>
       <c r="S667" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58081,7 +58081,7 @@
       </c>
       <c r="S668" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58166,7 +58166,7 @@
       </c>
       <c r="S669" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58251,7 +58251,7 @@
       </c>
       <c r="S670" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58340,7 +58340,7 @@
       </c>
       <c r="S671" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58429,7 +58429,7 @@
       </c>
       <c r="S672" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58518,7 +58518,7 @@
       </c>
       <c r="S673" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58607,7 +58607,7 @@
       </c>
       <c r="S674" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58696,7 +58696,7 @@
       </c>
       <c r="S675" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58785,7 +58785,7 @@
       </c>
       <c r="S676" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58874,7 +58874,7 @@
       </c>
       <c r="S677" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58963,7 +58963,7 @@
       </c>
       <c r="S678" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59052,7 +59052,7 @@
       </c>
       <c r="S679" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59141,7 +59141,7 @@
       </c>
       <c r="S680" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59230,7 +59230,7 @@
       </c>
       <c r="S681" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59319,7 +59319,7 @@
       </c>
       <c r="S682" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59408,7 +59408,7 @@
       </c>
       <c r="S683" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59497,7 +59497,7 @@
       </c>
       <c r="S684" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59586,7 +59586,7 @@
       </c>
       <c r="S685" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59675,7 +59675,7 @@
       </c>
       <c r="S686" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59764,7 +59764,7 @@
       </c>
       <c r="S687" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59853,7 +59853,7 @@
       </c>
       <c r="S688" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59942,7 +59942,7 @@
       </c>
       <c r="S689" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -60031,7 +60031,7 @@
       </c>
       <c r="S690" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -60120,7 +60120,7 @@
       </c>
       <c r="S691" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -60209,7 +60209,7 @@
       </c>
       <c r="S692" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="S693" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -60387,7 +60387,7 @@
       </c>
       <c r="S694" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -60476,7 +60476,7 @@
       </c>
       <c r="S695" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -60565,7 +60565,7 @@
       </c>
       <c r="S696" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -60654,7 +60654,7 @@
       </c>
       <c r="S697" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -60743,7 +60743,7 @@
       </c>
       <c r="S698" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -60832,7 +60832,7 @@
       </c>
       <c r="S699" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -60921,7 +60921,7 @@
       </c>
       <c r="S700" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -61010,7 +61010,7 @@
       </c>
       <c r="S701" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -61099,7 +61099,7 @@
       </c>
       <c r="S702" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -61188,7 +61188,7 @@
       </c>
       <c r="S703" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -61277,7 +61277,7 @@
       </c>
       <c r="S704" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -61366,7 +61366,7 @@
       </c>
       <c r="S705" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -61455,7 +61455,7 @@
       </c>
       <c r="S706" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -61544,7 +61544,7 @@
       </c>
       <c r="S707" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -61633,7 +61633,7 @@
       </c>
       <c r="S708" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -61722,7 +61722,7 @@
       </c>
       <c r="S709" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -61811,7 +61811,7 @@
       </c>
       <c r="S710" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -61900,7 +61900,7 @@
       </c>
       <c r="S711" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -61989,7 +61989,7 @@
       </c>
       <c r="S712" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -62078,7 +62078,7 @@
       </c>
       <c r="S713" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -62167,7 +62167,7 @@
       </c>
       <c r="S714" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -62256,7 +62256,7 @@
       </c>
       <c r="S715" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -62345,7 +62345,7 @@
       </c>
       <c r="S716" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -62434,7 +62434,7 @@
       </c>
       <c r="S717" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -62523,7 +62523,7 @@
       </c>
       <c r="S718" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -62612,7 +62612,7 @@
       </c>
       <c r="S719" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -62701,7 +62701,7 @@
       </c>
       <c r="S720" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -62786,7 +62786,7 @@
       </c>
       <c r="S721" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -62871,7 +62871,7 @@
       </c>
       <c r="S722" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -62956,7 +62956,7 @@
       </c>
       <c r="S723" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -63041,7 +63041,7 @@
       </c>
       <c r="S724" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -63126,7 +63126,7 @@
       </c>
       <c r="S725" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -63211,7 +63211,7 @@
       </c>
       <c r="S726" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -63296,7 +63296,7 @@
       </c>
       <c r="S727" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -63381,7 +63381,7 @@
       </c>
       <c r="S728" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -63466,7 +63466,7 @@
       </c>
       <c r="S729" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -63551,7 +63551,7 @@
       </c>
       <c r="S730" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -63636,7 +63636,7 @@
       </c>
       <c r="S731" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -63721,7 +63721,7 @@
       </c>
       <c r="S732" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -63806,7 +63806,7 @@
       </c>
       <c r="S733" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -63891,7 +63891,7 @@
       </c>
       <c r="S734" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -63976,7 +63976,7 @@
       </c>
       <c r="S735" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -64061,7 +64061,7 @@
       </c>
       <c r="S736" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -64146,7 +64146,7 @@
       </c>
       <c r="S737" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -64231,7 +64231,7 @@
       </c>
       <c r="S738" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -64316,7 +64316,7 @@
       </c>
       <c r="S739" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -64401,7 +64401,7 @@
       </c>
       <c r="S740" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -64486,7 +64486,7 @@
       </c>
       <c r="S741" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -64571,7 +64571,7 @@
       </c>
       <c r="S742" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -64660,7 +64660,7 @@
       </c>
       <c r="S743" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -64749,7 +64749,7 @@
       </c>
       <c r="S744" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -64838,7 +64838,7 @@
       </c>
       <c r="S745" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -64927,7 +64927,7 @@
       </c>
       <c r="S746" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -65016,7 +65016,7 @@
       </c>
       <c r="S747" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -65105,7 +65105,7 @@
       </c>
       <c r="S748" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -65194,7 +65194,7 @@
       </c>
       <c r="S749" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -65283,7 +65283,7 @@
       </c>
       <c r="S750" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -65372,7 +65372,7 @@
       </c>
       <c r="S751" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -65461,7 +65461,7 @@
       </c>
       <c r="S752" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -65550,7 +65550,7 @@
       </c>
       <c r="S753" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -65639,7 +65639,7 @@
       </c>
       <c r="S754" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -65728,7 +65728,7 @@
       </c>
       <c r="S755" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -65817,7 +65817,7 @@
       </c>
       <c r="S756" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -65906,7 +65906,7 @@
       </c>
       <c r="S757" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -65995,7 +65995,7 @@
       </c>
       <c r="S758" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -66084,7 +66084,7 @@
       </c>
       <c r="S759" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -66173,7 +66173,7 @@
       </c>
       <c r="S760" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -66262,7 +66262,7 @@
       </c>
       <c r="S761" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -66351,7 +66351,7 @@
       </c>
       <c r="S762" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -66436,7 +66436,7 @@
       </c>
       <c r="S763" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -66521,7 +66521,7 @@
       </c>
       <c r="S764" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -66606,7 +66606,7 @@
       </c>
       <c r="S765" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -66691,7 +66691,7 @@
       </c>
       <c r="S766" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -66776,7 +66776,7 @@
       </c>
       <c r="S767" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -66861,7 +66861,7 @@
       </c>
       <c r="S768" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -66946,7 +66946,7 @@
       </c>
       <c r="S769" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -67031,7 +67031,7 @@
       </c>
       <c r="S770" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -67116,7 +67116,7 @@
       </c>
       <c r="S771" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -67201,7 +67201,7 @@
       </c>
       <c r="S772" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -67286,7 +67286,7 @@
       </c>
       <c r="S773" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -67375,7 +67375,7 @@
       </c>
       <c r="S774" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -67464,7 +67464,7 @@
       </c>
       <c r="S775" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -67553,7 +67553,7 @@
       </c>
       <c r="S776" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -67642,7 +67642,7 @@
       </c>
       <c r="S777" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -67731,7 +67731,7 @@
       </c>
       <c r="S778" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -67820,7 +67820,7 @@
       </c>
       <c r="S779" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -67909,7 +67909,7 @@
       </c>
       <c r="S780" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -67998,7 +67998,7 @@
       </c>
       <c r="S781" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -68087,7 +68087,7 @@
       </c>
       <c r="S782" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -68176,7 +68176,7 @@
       </c>
       <c r="S783" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -68261,7 +68261,7 @@
       </c>
       <c r="S784" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -68346,7 +68346,7 @@
       </c>
       <c r="S785" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -68431,7 +68431,7 @@
       </c>
       <c r="S786" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -68516,7 +68516,7 @@
       </c>
       <c r="S787" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -68601,7 +68601,7 @@
       </c>
       <c r="S788" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -68686,7 +68686,7 @@
       </c>
       <c r="S789" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -68771,7 +68771,7 @@
       </c>
       <c r="S790" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -68856,7 +68856,7 @@
       </c>
       <c r="S791" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -68941,7 +68941,7 @@
       </c>
       <c r="S792" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -69026,7 +69026,7 @@
       </c>
       <c r="S793" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -69111,7 +69111,7 @@
       </c>
       <c r="S794" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -69200,7 +69200,7 @@
       </c>
       <c r="S795" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -69289,7 +69289,7 @@
       </c>
       <c r="S796" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -69378,7 +69378,7 @@
       </c>
       <c r="S797" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -69467,7 +69467,7 @@
       </c>
       <c r="S798" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -69556,7 +69556,7 @@
       </c>
       <c r="S799" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -69645,7 +69645,7 @@
       </c>
       <c r="S800" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -69734,7 +69734,7 @@
       </c>
       <c r="S801" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -69823,7 +69823,7 @@
       </c>
       <c r="S802" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -69912,7 +69912,7 @@
       </c>
       <c r="S803" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -70001,7 +70001,7 @@
       </c>
       <c r="S804" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -70086,7 +70086,7 @@
       </c>
       <c r="S805" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -70171,7 +70171,7 @@
       </c>
       <c r="S806" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -70256,7 +70256,7 @@
       </c>
       <c r="S807" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -70341,7 +70341,7 @@
       </c>
       <c r="S808" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -70426,7 +70426,7 @@
       </c>
       <c r="S809" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -70511,7 +70511,7 @@
       </c>
       <c r="S810" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -70596,7 +70596,7 @@
       </c>
       <c r="S811" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -70681,7 +70681,7 @@
       </c>
       <c r="S812" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -70766,7 +70766,7 @@
       </c>
       <c r="S813" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -70851,7 +70851,7 @@
       </c>
       <c r="S814" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -70936,7 +70936,7 @@
       </c>
       <c r="S815" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -71021,7 +71021,7 @@
       </c>
       <c r="S816" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -71106,7 +71106,7 @@
       </c>
       <c r="S817" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -71191,7 +71191,7 @@
       </c>
       <c r="S818" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -71276,7 +71276,7 @@
       </c>
       <c r="S819" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -71361,7 +71361,7 @@
       </c>
       <c r="S820" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -71446,7 +71446,7 @@
       </c>
       <c r="S821" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -71531,7 +71531,7 @@
       </c>
       <c r="S822" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -71616,7 +71616,7 @@
       </c>
       <c r="S823" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -71701,7 +71701,7 @@
       </c>
       <c r="S824" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -71786,7 +71786,7 @@
       </c>
       <c r="S825" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -71871,7 +71871,7 @@
       </c>
       <c r="S826" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -71960,7 +71960,7 @@
       </c>
       <c r="S827" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -72049,7 +72049,7 @@
       </c>
       <c r="S828" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -72138,7 +72138,7 @@
       </c>
       <c r="S829" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -72227,7 +72227,7 @@
       </c>
       <c r="S830" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -72316,7 +72316,7 @@
       </c>
       <c r="S831" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -72405,7 +72405,7 @@
       </c>
       <c r="S832" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -72494,7 +72494,7 @@
       </c>
       <c r="S833" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -72583,7 +72583,7 @@
       </c>
       <c r="S834" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -72672,7 +72672,7 @@
       </c>
       <c r="S835" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -72761,7 +72761,7 @@
       </c>
       <c r="S836" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -72850,7 +72850,7 @@
       </c>
       <c r="S837" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -72939,7 +72939,7 @@
       </c>
       <c r="S838" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -73028,7 +73028,7 @@
       </c>
       <c r="S839" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -73117,7 +73117,7 @@
       </c>
       <c r="S840" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -73206,7 +73206,7 @@
       </c>
       <c r="S841" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -73295,7 +73295,7 @@
       </c>
       <c r="S842" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -73384,7 +73384,7 @@
       </c>
       <c r="S843" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -73473,7 +73473,7 @@
       </c>
       <c r="S844" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -73562,7 +73562,7 @@
       </c>
       <c r="S845" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -73651,7 +73651,7 @@
       </c>
       <c r="S846" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -73736,7 +73736,7 @@
       </c>
       <c r="S847" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -73821,7 +73821,7 @@
       </c>
       <c r="S848" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -73906,7 +73906,7 @@
       </c>
       <c r="S849" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -73991,7 +73991,7 @@
       </c>
       <c r="S850" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -74076,7 +74076,7 @@
       </c>
       <c r="S851" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -74161,7 +74161,7 @@
       </c>
       <c r="S852" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -74246,7 +74246,7 @@
       </c>
       <c r="S853" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -74331,7 +74331,7 @@
       </c>
       <c r="S854" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -74416,7 +74416,7 @@
       </c>
       <c r="S855" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -74501,7 +74501,7 @@
       </c>
       <c r="S856" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -74586,7 +74586,7 @@
       </c>
       <c r="S857" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -74671,7 +74671,7 @@
       </c>
       <c r="S858" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -74756,7 +74756,7 @@
       </c>
       <c r="S859" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -74841,7 +74841,7 @@
       </c>
       <c r="S860" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -74926,7 +74926,7 @@
       </c>
       <c r="S861" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -75011,7 +75011,7 @@
       </c>
       <c r="S862" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -75096,7 +75096,7 @@
       </c>
       <c r="S863" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -75181,7 +75181,7 @@
       </c>
       <c r="S864" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -75266,7 +75266,7 @@
       </c>
       <c r="S865" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -75351,7 +75351,7 @@
       </c>
       <c r="S866" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -75436,7 +75436,7 @@
       </c>
       <c r="S867" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -75521,7 +75521,7 @@
       </c>
       <c r="S868" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -75610,7 +75610,7 @@
       </c>
       <c r="S869" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -75699,7 +75699,7 @@
       </c>
       <c r="S870" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -75788,7 +75788,7 @@
       </c>
       <c r="S871" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -75877,7 +75877,7 @@
       </c>
       <c r="S872" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -75966,7 +75966,7 @@
       </c>
       <c r="S873" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -76055,7 +76055,7 @@
       </c>
       <c r="S874" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -76144,7 +76144,7 @@
       </c>
       <c r="S875" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -76233,7 +76233,7 @@
       </c>
       <c r="S876" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -76322,7 +76322,7 @@
       </c>
       <c r="S877" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -76411,7 +76411,7 @@
       </c>
       <c r="S878" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -76500,7 +76500,7 @@
       </c>
       <c r="S879" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -76589,7 +76589,7 @@
       </c>
       <c r="S880" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -76678,7 +76678,7 @@
       </c>
       <c r="S881" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -76767,7 +76767,7 @@
       </c>
       <c r="S882" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -76856,7 +76856,7 @@
       </c>
       <c r="S883" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -76945,7 +76945,7 @@
       </c>
       <c r="S884" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -77034,7 +77034,7 @@
       </c>
       <c r="S885" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -77123,7 +77123,7 @@
       </c>
       <c r="S886" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -77212,7 +77212,7 @@
       </c>
       <c r="S887" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -77301,7 +77301,7 @@
       </c>
       <c r="S888" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -77433,7 +77433,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -77513,7 +77513,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-07-22T15:17:12Z"}</t>
+          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-07-22T21:35:45Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12625,7 +12625,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13936,7 +13936,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14446,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15041,7 +15041,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15296,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16008,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17161,7 +17161,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17416,7 +17416,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17501,7 +17501,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17586,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17671,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17841,7 +17841,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18100,7 +18100,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18367,7 +18367,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18812,7 +18812,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19326,7 +19326,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20176,7 +20176,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20261,7 +20261,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20686,7 +20686,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20941,7 +20941,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21026,7 +21026,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21281,7 +21281,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21536,7 +21536,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21706,7 +21706,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21795,7 +21795,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22062,7 +22062,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22151,7 +22151,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22240,7 +22240,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22507,7 +22507,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22596,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22685,7 +22685,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22774,7 +22774,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22952,7 +22952,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23041,7 +23041,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23130,7 +23130,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23308,7 +23308,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23397,7 +23397,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23486,7 +23486,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23575,7 +23575,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23753,7 +23753,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24198,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24287,7 +24287,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24376,7 +24376,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24461,7 +24461,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24716,7 +24716,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24886,7 +24886,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24971,7 +24971,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25056,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25226,7 +25226,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25396,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25566,7 +25566,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25736,7 +25736,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25906,7 +25906,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26076,7 +26076,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26161,7 +26161,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26335,7 +26335,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26424,7 +26424,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26602,7 +26602,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26780,7 +26780,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26869,7 +26869,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26958,7 +26958,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27225,7 +27225,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27403,7 +27403,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27492,7 +27492,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27670,7 +27670,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27759,7 +27759,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27848,7 +27848,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27937,7 +27937,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28026,7 +28026,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28196,7 +28196,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28281,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28366,7 +28366,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28451,7 +28451,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28876,7 +28876,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29046,7 +29046,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29216,7 +29216,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29301,7 +29301,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29386,7 +29386,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29471,7 +29471,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29556,7 +29556,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29641,7 +29641,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29726,7 +29726,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29811,7 +29811,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29985,7 +29985,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30341,7 +30341,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30430,7 +30430,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30608,7 +30608,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31231,7 +31231,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31498,7 +31498,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31587,7 +31587,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31676,7 +31676,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31761,7 +31761,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31846,7 +31846,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31931,7 +31931,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32101,7 +32101,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32186,7 +32186,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32271,7 +32271,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32356,7 +32356,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32441,7 +32441,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32526,7 +32526,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32611,7 +32611,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32696,7 +32696,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32951,7 +32951,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33036,7 +33036,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33291,7 +33291,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33376,7 +33376,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33461,7 +33461,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33724,7 +33724,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33813,7 +33813,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33902,7 +33902,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33991,7 +33991,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34080,7 +34080,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34169,7 +34169,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34258,7 +34258,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34347,7 +34347,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34436,7 +34436,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34525,7 +34525,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34614,7 +34614,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34703,7 +34703,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34881,7 +34881,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35148,7 +35148,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35237,7 +35237,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35326,7 +35326,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35411,7 +35411,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35496,7 +35496,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35581,7 +35581,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35836,7 +35836,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36006,7 +36006,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36091,7 +36091,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36176,7 +36176,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36261,7 +36261,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36350,7 +36350,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36439,7 +36439,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36706,7 +36706,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36795,7 +36795,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36884,7 +36884,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36973,7 +36973,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37062,7 +37062,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37151,7 +37151,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37236,7 +37236,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37321,7 +37321,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37491,7 +37491,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37576,7 +37576,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37661,7 +37661,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37746,7 +37746,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37831,7 +37831,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38001,7 +38001,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38086,7 +38086,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38256,7 +38256,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38341,7 +38341,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38426,7 +38426,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38511,7 +38511,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38596,7 +38596,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38681,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38766,7 +38766,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38851,7 +38851,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38936,7 +38936,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39021,7 +39021,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39110,7 +39110,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39199,7 +39199,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39288,7 +39288,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39377,7 +39377,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39466,7 +39466,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39644,7 +39644,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39822,7 +39822,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39911,7 +39911,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40000,7 +40000,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40089,7 +40089,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40178,7 +40178,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40267,7 +40267,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40445,7 +40445,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40534,7 +40534,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40623,7 +40623,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40712,7 +40712,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40886,7 +40886,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40971,7 +40971,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41141,7 +41141,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41226,7 +41226,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41311,7 +41311,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41396,7 +41396,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41481,7 +41481,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41566,7 +41566,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41651,7 +41651,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41736,7 +41736,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41825,7 +41825,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41914,7 +41914,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42003,7 +42003,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42092,7 +42092,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42181,7 +42181,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42270,7 +42270,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42359,7 +42359,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42448,7 +42448,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42537,7 +42537,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42626,7 +42626,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42711,7 +42711,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42796,7 +42796,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42881,7 +42881,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43051,7 +43051,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43221,7 +43221,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43306,7 +43306,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43391,7 +43391,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43476,7 +43476,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43561,7 +43561,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43646,7 +43646,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43731,7 +43731,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43816,7 +43816,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43901,7 +43901,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43986,7 +43986,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44071,7 +44071,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44156,7 +44156,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44241,7 +44241,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44411,7 +44411,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44496,7 +44496,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44585,7 +44585,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44674,7 +44674,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44763,7 +44763,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44852,7 +44852,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44941,7 +44941,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45030,7 +45030,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45119,7 +45119,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45208,7 +45208,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45297,7 +45297,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45386,7 +45386,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45475,7 +45475,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45564,7 +45564,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45653,7 +45653,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45742,7 +45742,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45831,7 +45831,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45920,7 +45920,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46009,7 +46009,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46098,7 +46098,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46187,7 +46187,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46276,7 +46276,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46361,7 +46361,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46446,7 +46446,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46531,7 +46531,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46616,7 +46616,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46701,7 +46701,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46786,7 +46786,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46871,7 +46871,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46956,7 +46956,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47041,7 +47041,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47126,7 +47126,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47211,7 +47211,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47300,7 +47300,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47389,7 +47389,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47478,7 +47478,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47567,7 +47567,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47656,7 +47656,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47745,7 +47745,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47834,7 +47834,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47923,7 +47923,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48012,7 +48012,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48101,7 +48101,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48186,7 +48186,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48271,7 +48271,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48356,7 +48356,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48441,7 +48441,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48526,7 +48526,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48696,7 +48696,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48781,7 +48781,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48866,7 +48866,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48951,7 +48951,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49036,7 +49036,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49125,7 +49125,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49214,7 +49214,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49303,7 +49303,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49392,7 +49392,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49481,7 +49481,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49570,7 +49570,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49659,7 +49659,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49748,7 +49748,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49837,7 +49837,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49926,7 +49926,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50011,7 +50011,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50096,7 +50096,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50181,7 +50181,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50266,7 +50266,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50436,7 +50436,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50521,7 +50521,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50606,7 +50606,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50691,7 +50691,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50776,7 +50776,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50861,7 +50861,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50946,7 +50946,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51031,7 +51031,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51116,7 +51116,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51201,7 +51201,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51286,7 +51286,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51371,7 +51371,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51456,7 +51456,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51541,7 +51541,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51626,7 +51626,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51711,7 +51711,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51796,7 +51796,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51885,7 +51885,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51974,7 +51974,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52063,7 +52063,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52152,7 +52152,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52241,7 +52241,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52330,7 +52330,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52419,7 +52419,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52508,7 +52508,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52597,7 +52597,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52686,7 +52686,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52775,7 +52775,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52864,7 +52864,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52953,7 +52953,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53042,7 +53042,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53131,7 +53131,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53220,7 +53220,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53309,7 +53309,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53398,7 +53398,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53487,7 +53487,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53576,7 +53576,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53661,7 +53661,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53746,7 +53746,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53831,7 +53831,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53916,7 +53916,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54001,7 +54001,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54086,7 +54086,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54171,7 +54171,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54256,7 +54256,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54426,7 +54426,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54511,7 +54511,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54596,7 +54596,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54681,7 +54681,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54766,7 +54766,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54851,7 +54851,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54936,7 +54936,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55021,7 +55021,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55106,7 +55106,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55191,7 +55191,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55276,7 +55276,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55361,7 +55361,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55446,7 +55446,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55531,7 +55531,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55616,7 +55616,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55701,7 +55701,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55786,7 +55786,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55871,7 +55871,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55956,7 +55956,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56041,7 +56041,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56126,7 +56126,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56211,7 +56211,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56296,7 +56296,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56381,7 +56381,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56466,7 +56466,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56551,7 +56551,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56636,7 +56636,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56721,7 +56721,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56806,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56891,7 +56891,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56976,7 +56976,7 @@
       </c>
       <c r="S655" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57061,7 +57061,7 @@
       </c>
       <c r="S656" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57146,7 +57146,7 @@
       </c>
       <c r="S657" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57231,7 +57231,7 @@
       </c>
       <c r="S658" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57316,7 +57316,7 @@
       </c>
       <c r="S659" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57401,7 +57401,7 @@
       </c>
       <c r="S660" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57486,7 +57486,7 @@
       </c>
       <c r="S661" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57571,7 +57571,7 @@
       </c>
       <c r="S662" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57656,7 +57656,7 @@
       </c>
       <c r="S663" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57741,7 +57741,7 @@
       </c>
       <c r="S664" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57826,7 +57826,7 @@
       </c>
       <c r="S665" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57911,7 +57911,7 @@
       </c>
       <c r="S666" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57996,7 +57996,7 @@
       </c>
       <c r="S667" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58081,7 +58081,7 @@
       </c>
       <c r="S668" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58166,7 +58166,7 @@
       </c>
       <c r="S669" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58251,7 +58251,7 @@
       </c>
       <c r="S670" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58340,7 +58340,7 @@
       </c>
       <c r="S671" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58429,7 +58429,7 @@
       </c>
       <c r="S672" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58518,7 +58518,7 @@
       </c>
       <c r="S673" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58607,7 +58607,7 @@
       </c>
       <c r="S674" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58696,7 +58696,7 @@
       </c>
       <c r="S675" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58785,7 +58785,7 @@
       </c>
       <c r="S676" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58874,7 +58874,7 @@
       </c>
       <c r="S677" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58963,7 +58963,7 @@
       </c>
       <c r="S678" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59052,7 +59052,7 @@
       </c>
       <c r="S679" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59141,7 +59141,7 @@
       </c>
       <c r="S680" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59230,7 +59230,7 @@
       </c>
       <c r="S681" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59319,7 +59319,7 @@
       </c>
       <c r="S682" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59408,7 +59408,7 @@
       </c>
       <c r="S683" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59497,7 +59497,7 @@
       </c>
       <c r="S684" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59586,7 +59586,7 @@
       </c>
       <c r="S685" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59675,7 +59675,7 @@
       </c>
       <c r="S686" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59764,7 +59764,7 @@
       </c>
       <c r="S687" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59853,7 +59853,7 @@
       </c>
       <c r="S688" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59942,7 +59942,7 @@
       </c>
       <c r="S689" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -60031,7 +60031,7 @@
       </c>
       <c r="S690" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -60120,7 +60120,7 @@
       </c>
       <c r="S691" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -60209,7 +60209,7 @@
       </c>
       <c r="S692" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="S693" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -60387,7 +60387,7 @@
       </c>
       <c r="S694" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -60476,7 +60476,7 @@
       </c>
       <c r="S695" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -60565,7 +60565,7 @@
       </c>
       <c r="S696" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -60654,7 +60654,7 @@
       </c>
       <c r="S697" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -60743,7 +60743,7 @@
       </c>
       <c r="S698" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -60832,7 +60832,7 @@
       </c>
       <c r="S699" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -60921,7 +60921,7 @@
       </c>
       <c r="S700" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -61010,7 +61010,7 @@
       </c>
       <c r="S701" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -61099,7 +61099,7 @@
       </c>
       <c r="S702" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -61188,7 +61188,7 @@
       </c>
       <c r="S703" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -61277,7 +61277,7 @@
       </c>
       <c r="S704" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -61366,7 +61366,7 @@
       </c>
       <c r="S705" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -61455,7 +61455,7 @@
       </c>
       <c r="S706" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -61544,7 +61544,7 @@
       </c>
       <c r="S707" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -61633,7 +61633,7 @@
       </c>
       <c r="S708" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -61722,7 +61722,7 @@
       </c>
       <c r="S709" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -61811,7 +61811,7 @@
       </c>
       <c r="S710" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -61900,7 +61900,7 @@
       </c>
       <c r="S711" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -61989,7 +61989,7 @@
       </c>
       <c r="S712" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -62078,7 +62078,7 @@
       </c>
       <c r="S713" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -62167,7 +62167,7 @@
       </c>
       <c r="S714" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -62256,7 +62256,7 @@
       </c>
       <c r="S715" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -62345,7 +62345,7 @@
       </c>
       <c r="S716" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -62434,7 +62434,7 @@
       </c>
       <c r="S717" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -62523,7 +62523,7 @@
       </c>
       <c r="S718" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -62612,7 +62612,7 @@
       </c>
       <c r="S719" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -62701,7 +62701,7 @@
       </c>
       <c r="S720" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -62786,7 +62786,7 @@
       </c>
       <c r="S721" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -62871,7 +62871,7 @@
       </c>
       <c r="S722" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -62956,7 +62956,7 @@
       </c>
       <c r="S723" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -63041,7 +63041,7 @@
       </c>
       <c r="S724" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -63126,7 +63126,7 @@
       </c>
       <c r="S725" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -63211,7 +63211,7 @@
       </c>
       <c r="S726" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -63296,7 +63296,7 @@
       </c>
       <c r="S727" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -63381,7 +63381,7 @@
       </c>
       <c r="S728" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -63466,7 +63466,7 @@
       </c>
       <c r="S729" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -63551,7 +63551,7 @@
       </c>
       <c r="S730" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -63636,7 +63636,7 @@
       </c>
       <c r="S731" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -63721,7 +63721,7 @@
       </c>
       <c r="S732" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -63806,7 +63806,7 @@
       </c>
       <c r="S733" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -63891,7 +63891,7 @@
       </c>
       <c r="S734" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -63976,7 +63976,7 @@
       </c>
       <c r="S735" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -64061,7 +64061,7 @@
       </c>
       <c r="S736" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -64146,7 +64146,7 @@
       </c>
       <c r="S737" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -64231,7 +64231,7 @@
       </c>
       <c r="S738" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -64316,7 +64316,7 @@
       </c>
       <c r="S739" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -64401,7 +64401,7 @@
       </c>
       <c r="S740" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -64486,7 +64486,7 @@
       </c>
       <c r="S741" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -64571,7 +64571,7 @@
       </c>
       <c r="S742" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -64660,7 +64660,7 @@
       </c>
       <c r="S743" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -64749,7 +64749,7 @@
       </c>
       <c r="S744" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -64838,7 +64838,7 @@
       </c>
       <c r="S745" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -64927,7 +64927,7 @@
       </c>
       <c r="S746" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -65016,7 +65016,7 @@
       </c>
       <c r="S747" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -65105,7 +65105,7 @@
       </c>
       <c r="S748" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -65194,7 +65194,7 @@
       </c>
       <c r="S749" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -65283,7 +65283,7 @@
       </c>
       <c r="S750" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -65372,7 +65372,7 @@
       </c>
       <c r="S751" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -65461,7 +65461,7 @@
       </c>
       <c r="S752" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -65550,7 +65550,7 @@
       </c>
       <c r="S753" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -65639,7 +65639,7 @@
       </c>
       <c r="S754" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -65728,7 +65728,7 @@
       </c>
       <c r="S755" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -65817,7 +65817,7 @@
       </c>
       <c r="S756" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -65906,7 +65906,7 @@
       </c>
       <c r="S757" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -65995,7 +65995,7 @@
       </c>
       <c r="S758" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -66084,7 +66084,7 @@
       </c>
       <c r="S759" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -66173,7 +66173,7 @@
       </c>
       <c r="S760" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -66262,7 +66262,7 @@
       </c>
       <c r="S761" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -66351,7 +66351,7 @@
       </c>
       <c r="S762" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -66436,7 +66436,7 @@
       </c>
       <c r="S763" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -66521,7 +66521,7 @@
       </c>
       <c r="S764" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -66606,7 +66606,7 @@
       </c>
       <c r="S765" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -66691,7 +66691,7 @@
       </c>
       <c r="S766" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -66776,7 +66776,7 @@
       </c>
       <c r="S767" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -66861,7 +66861,7 @@
       </c>
       <c r="S768" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -66946,7 +66946,7 @@
       </c>
       <c r="S769" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -67031,7 +67031,7 @@
       </c>
       <c r="S770" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -67116,7 +67116,7 @@
       </c>
       <c r="S771" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -67201,7 +67201,7 @@
       </c>
       <c r="S772" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -67286,7 +67286,7 @@
       </c>
       <c r="S773" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -67375,7 +67375,7 @@
       </c>
       <c r="S774" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -67464,7 +67464,7 @@
       </c>
       <c r="S775" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -67553,7 +67553,7 @@
       </c>
       <c r="S776" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -67642,7 +67642,7 @@
       </c>
       <c r="S777" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -67731,7 +67731,7 @@
       </c>
       <c r="S778" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -67820,7 +67820,7 @@
       </c>
       <c r="S779" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -67909,7 +67909,7 @@
       </c>
       <c r="S780" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -67998,7 +67998,7 @@
       </c>
       <c r="S781" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -68087,7 +68087,7 @@
       </c>
       <c r="S782" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -68176,7 +68176,7 @@
       </c>
       <c r="S783" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -68261,7 +68261,7 @@
       </c>
       <c r="S784" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -68346,7 +68346,7 @@
       </c>
       <c r="S785" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -68431,7 +68431,7 @@
       </c>
       <c r="S786" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -68516,7 +68516,7 @@
       </c>
       <c r="S787" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -68601,7 +68601,7 @@
       </c>
       <c r="S788" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -68686,7 +68686,7 @@
       </c>
       <c r="S789" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -68771,7 +68771,7 @@
       </c>
       <c r="S790" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -68856,7 +68856,7 @@
       </c>
       <c r="S791" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -68941,7 +68941,7 @@
       </c>
       <c r="S792" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -69026,7 +69026,7 @@
       </c>
       <c r="S793" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -69111,7 +69111,7 @@
       </c>
       <c r="S794" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -69200,7 +69200,7 @@
       </c>
       <c r="S795" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -69289,7 +69289,7 @@
       </c>
       <c r="S796" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -69378,7 +69378,7 @@
       </c>
       <c r="S797" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -69467,7 +69467,7 @@
       </c>
       <c r="S798" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -69556,7 +69556,7 @@
       </c>
       <c r="S799" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -69645,7 +69645,7 @@
       </c>
       <c r="S800" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -69734,7 +69734,7 @@
       </c>
       <c r="S801" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -69823,7 +69823,7 @@
       </c>
       <c r="S802" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -69912,7 +69912,7 @@
       </c>
       <c r="S803" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -70001,7 +70001,7 @@
       </c>
       <c r="S804" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -70086,7 +70086,7 @@
       </c>
       <c r="S805" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -70171,7 +70171,7 @@
       </c>
       <c r="S806" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -70256,7 +70256,7 @@
       </c>
       <c r="S807" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -70341,7 +70341,7 @@
       </c>
       <c r="S808" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -70426,7 +70426,7 @@
       </c>
       <c r="S809" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -70511,7 +70511,7 @@
       </c>
       <c r="S810" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -70596,7 +70596,7 @@
       </c>
       <c r="S811" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -70681,7 +70681,7 @@
       </c>
       <c r="S812" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -70766,7 +70766,7 @@
       </c>
       <c r="S813" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -70851,7 +70851,7 @@
       </c>
       <c r="S814" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -70936,7 +70936,7 @@
       </c>
       <c r="S815" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -71021,7 +71021,7 @@
       </c>
       <c r="S816" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -71106,7 +71106,7 @@
       </c>
       <c r="S817" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -71191,7 +71191,7 @@
       </c>
       <c r="S818" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -71276,7 +71276,7 @@
       </c>
       <c r="S819" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -71361,7 +71361,7 @@
       </c>
       <c r="S820" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -71446,7 +71446,7 @@
       </c>
       <c r="S821" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -71531,7 +71531,7 @@
       </c>
       <c r="S822" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -71616,7 +71616,7 @@
       </c>
       <c r="S823" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -71701,7 +71701,7 @@
       </c>
       <c r="S824" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -71786,7 +71786,7 @@
       </c>
       <c r="S825" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -71871,7 +71871,7 @@
       </c>
       <c r="S826" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -71960,7 +71960,7 @@
       </c>
       <c r="S827" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -72049,7 +72049,7 @@
       </c>
       <c r="S828" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -72138,7 +72138,7 @@
       </c>
       <c r="S829" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -72227,7 +72227,7 @@
       </c>
       <c r="S830" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -72316,7 +72316,7 @@
       </c>
       <c r="S831" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -72405,7 +72405,7 @@
       </c>
       <c r="S832" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -72494,7 +72494,7 @@
       </c>
       <c r="S833" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -72583,7 +72583,7 @@
       </c>
       <c r="S834" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -72672,7 +72672,7 @@
       </c>
       <c r="S835" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -72761,7 +72761,7 @@
       </c>
       <c r="S836" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -72850,7 +72850,7 @@
       </c>
       <c r="S837" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -72939,7 +72939,7 @@
       </c>
       <c r="S838" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -73028,7 +73028,7 @@
       </c>
       <c r="S839" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -73117,7 +73117,7 @@
       </c>
       <c r="S840" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -73206,7 +73206,7 @@
       </c>
       <c r="S841" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -73295,7 +73295,7 @@
       </c>
       <c r="S842" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -73384,7 +73384,7 @@
       </c>
       <c r="S843" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -73473,7 +73473,7 @@
       </c>
       <c r="S844" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -73562,7 +73562,7 @@
       </c>
       <c r="S845" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -73651,7 +73651,7 @@
       </c>
       <c r="S846" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -73736,7 +73736,7 @@
       </c>
       <c r="S847" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -73821,7 +73821,7 @@
       </c>
       <c r="S848" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -73906,7 +73906,7 @@
       </c>
       <c r="S849" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -73991,7 +73991,7 @@
       </c>
       <c r="S850" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -74076,7 +74076,7 @@
       </c>
       <c r="S851" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -74161,7 +74161,7 @@
       </c>
       <c r="S852" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -74246,7 +74246,7 @@
       </c>
       <c r="S853" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -74331,7 +74331,7 @@
       </c>
       <c r="S854" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -74416,7 +74416,7 @@
       </c>
       <c r="S855" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -74501,7 +74501,7 @@
       </c>
       <c r="S856" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -74586,7 +74586,7 @@
       </c>
       <c r="S857" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -74671,7 +74671,7 @@
       </c>
       <c r="S858" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -74756,7 +74756,7 @@
       </c>
       <c r="S859" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -74841,7 +74841,7 @@
       </c>
       <c r="S860" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -74926,7 +74926,7 @@
       </c>
       <c r="S861" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -75011,7 +75011,7 @@
       </c>
       <c r="S862" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -75096,7 +75096,7 @@
       </c>
       <c r="S863" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -75181,7 +75181,7 @@
       </c>
       <c r="S864" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -75266,7 +75266,7 @@
       </c>
       <c r="S865" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -75351,7 +75351,7 @@
       </c>
       <c r="S866" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -75436,7 +75436,7 @@
       </c>
       <c r="S867" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -75521,7 +75521,7 @@
       </c>
       <c r="S868" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -75610,7 +75610,7 @@
       </c>
       <c r="S869" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -75699,7 +75699,7 @@
       </c>
       <c r="S870" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -75788,7 +75788,7 @@
       </c>
       <c r="S871" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -75877,7 +75877,7 @@
       </c>
       <c r="S872" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -75966,7 +75966,7 @@
       </c>
       <c r="S873" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -76055,7 +76055,7 @@
       </c>
       <c r="S874" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -76144,7 +76144,7 @@
       </c>
       <c r="S875" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -76233,7 +76233,7 @@
       </c>
       <c r="S876" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -76322,7 +76322,7 @@
       </c>
       <c r="S877" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -76411,7 +76411,7 @@
       </c>
       <c r="S878" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -76500,7 +76500,7 @@
       </c>
       <c r="S879" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -76589,7 +76589,7 @@
       </c>
       <c r="S880" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -76678,7 +76678,7 @@
       </c>
       <c r="S881" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -76767,7 +76767,7 @@
       </c>
       <c r="S882" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -76856,7 +76856,7 @@
       </c>
       <c r="S883" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -76945,7 +76945,7 @@
       </c>
       <c r="S884" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -77034,7 +77034,7 @@
       </c>
       <c r="S885" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -77123,7 +77123,7 @@
       </c>
       <c r="S886" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -77212,7 +77212,7 @@
       </c>
       <c r="S887" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -77301,7 +77301,7 @@
       </c>
       <c r="S888" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -77433,7 +77433,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -77513,7 +77513,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-07-23T21:35:03Z"}</t>
+          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-07-24T21:36:09Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12625,7 +12625,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13936,7 +13936,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14446,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15041,7 +15041,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15296,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16008,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17161,7 +17161,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17416,7 +17416,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17501,7 +17501,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17586,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17671,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17841,7 +17841,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18100,7 +18100,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18367,7 +18367,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18812,7 +18812,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19326,7 +19326,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20176,7 +20176,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20261,7 +20261,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20686,7 +20686,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20941,7 +20941,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21026,7 +21026,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21281,7 +21281,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21536,7 +21536,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21706,7 +21706,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21795,7 +21795,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22062,7 +22062,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22151,7 +22151,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22240,7 +22240,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22507,7 +22507,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22596,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22685,7 +22685,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22774,7 +22774,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22952,7 +22952,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23041,7 +23041,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23130,7 +23130,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23308,7 +23308,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23397,7 +23397,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23486,7 +23486,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23575,7 +23575,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23753,7 +23753,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24198,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24287,7 +24287,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24376,7 +24376,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24461,7 +24461,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24716,7 +24716,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24886,7 +24886,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24971,7 +24971,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25056,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25226,7 +25226,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25396,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25566,7 +25566,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25736,7 +25736,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25906,7 +25906,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26076,7 +26076,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26161,7 +26161,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26335,7 +26335,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26424,7 +26424,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26602,7 +26602,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26780,7 +26780,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26869,7 +26869,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26958,7 +26958,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27225,7 +27225,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27403,7 +27403,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27492,7 +27492,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27670,7 +27670,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27759,7 +27759,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27848,7 +27848,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27937,7 +27937,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28026,7 +28026,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28196,7 +28196,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28281,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28366,7 +28366,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28451,7 +28451,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28876,7 +28876,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29046,7 +29046,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29216,7 +29216,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29301,7 +29301,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29386,7 +29386,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29471,7 +29471,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29556,7 +29556,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29641,7 +29641,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29726,7 +29726,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29811,7 +29811,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29985,7 +29985,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30341,7 +30341,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30430,7 +30430,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30608,7 +30608,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31231,7 +31231,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31498,7 +31498,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31587,7 +31587,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31676,7 +31676,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31761,7 +31761,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31846,7 +31846,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31931,7 +31931,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32101,7 +32101,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32186,7 +32186,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32271,7 +32271,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32356,7 +32356,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32441,7 +32441,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32526,7 +32526,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32611,7 +32611,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32696,7 +32696,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32951,7 +32951,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33036,7 +33036,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33291,7 +33291,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33376,7 +33376,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33461,7 +33461,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33724,7 +33724,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33813,7 +33813,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33902,7 +33902,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33991,7 +33991,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34080,7 +34080,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34169,7 +34169,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34258,7 +34258,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34347,7 +34347,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34436,7 +34436,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34525,7 +34525,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34614,7 +34614,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34703,7 +34703,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34881,7 +34881,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35148,7 +35148,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35237,7 +35237,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35326,7 +35326,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35411,7 +35411,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35496,7 +35496,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35581,7 +35581,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35836,7 +35836,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36006,7 +36006,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36091,7 +36091,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36176,7 +36176,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36261,7 +36261,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36350,7 +36350,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36439,7 +36439,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36706,7 +36706,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36795,7 +36795,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36884,7 +36884,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36973,7 +36973,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37062,7 +37062,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37151,7 +37151,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37236,7 +37236,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37321,7 +37321,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37491,7 +37491,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37576,7 +37576,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37661,7 +37661,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37746,7 +37746,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37831,7 +37831,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38001,7 +38001,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38086,7 +38086,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38256,7 +38256,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38341,7 +38341,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38426,7 +38426,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38511,7 +38511,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38596,7 +38596,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38681,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38766,7 +38766,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38851,7 +38851,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38936,7 +38936,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39021,7 +39021,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39110,7 +39110,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39199,7 +39199,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39288,7 +39288,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39377,7 +39377,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39466,7 +39466,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39644,7 +39644,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39822,7 +39822,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39911,7 +39911,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40000,7 +40000,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40089,7 +40089,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40178,7 +40178,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40267,7 +40267,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40445,7 +40445,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40534,7 +40534,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40623,7 +40623,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40712,7 +40712,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40886,7 +40886,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40971,7 +40971,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41141,7 +41141,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41226,7 +41226,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41311,7 +41311,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41396,7 +41396,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41481,7 +41481,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41566,7 +41566,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41651,7 +41651,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41736,7 +41736,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41825,7 +41825,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41914,7 +41914,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42003,7 +42003,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42092,7 +42092,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42181,7 +42181,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42270,7 +42270,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42359,7 +42359,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42448,7 +42448,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42537,7 +42537,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42626,7 +42626,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42711,7 +42711,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42796,7 +42796,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42881,7 +42881,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43051,7 +43051,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43221,7 +43221,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43306,7 +43306,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43391,7 +43391,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43476,7 +43476,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43561,7 +43561,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43646,7 +43646,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43731,7 +43731,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43816,7 +43816,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43901,7 +43901,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43986,7 +43986,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44071,7 +44071,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44156,7 +44156,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44241,7 +44241,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44411,7 +44411,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44496,7 +44496,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44585,7 +44585,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44674,7 +44674,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44763,7 +44763,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44852,7 +44852,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44941,7 +44941,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45030,7 +45030,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45119,7 +45119,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45208,7 +45208,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45297,7 +45297,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45386,7 +45386,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45475,7 +45475,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45564,7 +45564,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45653,7 +45653,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45742,7 +45742,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45831,7 +45831,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45920,7 +45920,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46009,7 +46009,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46098,7 +46098,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46187,7 +46187,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46276,7 +46276,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46361,7 +46361,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46446,7 +46446,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46531,7 +46531,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46616,7 +46616,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46701,7 +46701,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46786,7 +46786,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46871,7 +46871,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46956,7 +46956,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47041,7 +47041,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47126,7 +47126,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47211,7 +47211,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47300,7 +47300,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47389,7 +47389,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47478,7 +47478,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47567,7 +47567,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47656,7 +47656,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47745,7 +47745,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47834,7 +47834,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47923,7 +47923,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48012,7 +48012,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48101,7 +48101,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48186,7 +48186,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48271,7 +48271,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48356,7 +48356,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48441,7 +48441,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48526,7 +48526,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48696,7 +48696,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48781,7 +48781,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48866,7 +48866,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48951,7 +48951,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49036,7 +49036,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49125,7 +49125,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49214,7 +49214,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49303,7 +49303,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49392,7 +49392,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49481,7 +49481,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49570,7 +49570,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49659,7 +49659,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49748,7 +49748,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49837,7 +49837,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49926,7 +49926,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50011,7 +50011,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50096,7 +50096,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50181,7 +50181,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50266,7 +50266,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50436,7 +50436,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50521,7 +50521,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50606,7 +50606,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50691,7 +50691,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50776,7 +50776,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50861,7 +50861,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50946,7 +50946,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51031,7 +51031,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51116,7 +51116,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51201,7 +51201,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51286,7 +51286,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51371,7 +51371,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51456,7 +51456,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51541,7 +51541,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51626,7 +51626,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51711,7 +51711,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51796,7 +51796,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51885,7 +51885,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51974,7 +51974,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52063,7 +52063,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52152,7 +52152,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52241,7 +52241,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52330,7 +52330,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52419,7 +52419,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52508,7 +52508,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52597,7 +52597,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52686,7 +52686,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52775,7 +52775,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52864,7 +52864,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52953,7 +52953,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53042,7 +53042,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53131,7 +53131,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53220,7 +53220,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53309,7 +53309,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53398,7 +53398,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53487,7 +53487,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53576,7 +53576,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53661,7 +53661,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53746,7 +53746,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53831,7 +53831,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53916,7 +53916,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54001,7 +54001,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54086,7 +54086,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54171,7 +54171,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54256,7 +54256,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54426,7 +54426,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54511,7 +54511,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54596,7 +54596,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54681,7 +54681,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54766,7 +54766,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54851,7 +54851,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54936,7 +54936,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55021,7 +55021,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55106,7 +55106,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55191,7 +55191,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55276,7 +55276,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55361,7 +55361,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55446,7 +55446,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55531,7 +55531,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55616,7 +55616,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55701,7 +55701,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55786,7 +55786,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55871,7 +55871,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55956,7 +55956,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56041,7 +56041,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56126,7 +56126,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56211,7 +56211,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56296,7 +56296,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56381,7 +56381,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56466,7 +56466,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56551,7 +56551,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56636,7 +56636,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56721,7 +56721,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56806,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56891,7 +56891,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56976,7 +56976,7 @@
       </c>
       <c r="S655" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57061,7 +57061,7 @@
       </c>
       <c r="S656" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57146,7 +57146,7 @@
       </c>
       <c r="S657" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57231,7 +57231,7 @@
       </c>
       <c r="S658" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57316,7 +57316,7 @@
       </c>
       <c r="S659" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57401,7 +57401,7 @@
       </c>
       <c r="S660" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57486,7 +57486,7 @@
       </c>
       <c r="S661" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57571,7 +57571,7 @@
       </c>
       <c r="S662" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57656,7 +57656,7 @@
       </c>
       <c r="S663" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57741,7 +57741,7 @@
       </c>
       <c r="S664" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57826,7 +57826,7 @@
       </c>
       <c r="S665" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57911,7 +57911,7 @@
       </c>
       <c r="S666" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57996,7 +57996,7 @@
       </c>
       <c r="S667" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58081,7 +58081,7 @@
       </c>
       <c r="S668" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58166,7 +58166,7 @@
       </c>
       <c r="S669" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58251,7 +58251,7 @@
       </c>
       <c r="S670" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58340,7 +58340,7 @@
       </c>
       <c r="S671" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58429,7 +58429,7 @@
       </c>
       <c r="S672" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58518,7 +58518,7 @@
       </c>
       <c r="S673" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58607,7 +58607,7 @@
       </c>
       <c r="S674" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58696,7 +58696,7 @@
       </c>
       <c r="S675" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58785,7 +58785,7 @@
       </c>
       <c r="S676" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58874,7 +58874,7 @@
       </c>
       <c r="S677" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58963,7 +58963,7 @@
       </c>
       <c r="S678" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59052,7 +59052,7 @@
       </c>
       <c r="S679" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59141,7 +59141,7 @@
       </c>
       <c r="S680" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59230,7 +59230,7 @@
       </c>
       <c r="S681" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59319,7 +59319,7 @@
       </c>
       <c r="S682" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59408,7 +59408,7 @@
       </c>
       <c r="S683" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59497,7 +59497,7 @@
       </c>
       <c r="S684" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59586,7 +59586,7 @@
       </c>
       <c r="S685" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59675,7 +59675,7 @@
       </c>
       <c r="S686" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59764,7 +59764,7 @@
       </c>
       <c r="S687" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59853,7 +59853,7 @@
       </c>
       <c r="S688" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59942,7 +59942,7 @@
       </c>
       <c r="S689" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -60031,7 +60031,7 @@
       </c>
       <c r="S690" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -60120,7 +60120,7 @@
       </c>
       <c r="S691" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -60209,7 +60209,7 @@
       </c>
       <c r="S692" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="S693" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -60387,7 +60387,7 @@
       </c>
       <c r="S694" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -60476,7 +60476,7 @@
       </c>
       <c r="S695" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -60565,7 +60565,7 @@
       </c>
       <c r="S696" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -60654,7 +60654,7 @@
       </c>
       <c r="S697" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -60743,7 +60743,7 @@
       </c>
       <c r="S698" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -60832,7 +60832,7 @@
       </c>
       <c r="S699" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -60921,7 +60921,7 @@
       </c>
       <c r="S700" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -61010,7 +61010,7 @@
       </c>
       <c r="S701" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -61099,7 +61099,7 @@
       </c>
       <c r="S702" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -61188,7 +61188,7 @@
       </c>
       <c r="S703" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -61277,7 +61277,7 @@
       </c>
       <c r="S704" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -61366,7 +61366,7 @@
       </c>
       <c r="S705" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -61455,7 +61455,7 @@
       </c>
       <c r="S706" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -61544,7 +61544,7 @@
       </c>
       <c r="S707" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -61633,7 +61633,7 @@
       </c>
       <c r="S708" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -61722,7 +61722,7 @@
       </c>
       <c r="S709" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -61811,7 +61811,7 @@
       </c>
       <c r="S710" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -61900,7 +61900,7 @@
       </c>
       <c r="S711" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -61989,7 +61989,7 @@
       </c>
       <c r="S712" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -62078,7 +62078,7 @@
       </c>
       <c r="S713" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -62167,7 +62167,7 @@
       </c>
       <c r="S714" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -62256,7 +62256,7 @@
       </c>
       <c r="S715" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -62345,7 +62345,7 @@
       </c>
       <c r="S716" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -62434,7 +62434,7 @@
       </c>
       <c r="S717" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -62523,7 +62523,7 @@
       </c>
       <c r="S718" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -62612,7 +62612,7 @@
       </c>
       <c r="S719" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -62701,7 +62701,7 @@
       </c>
       <c r="S720" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -62786,7 +62786,7 @@
       </c>
       <c r="S721" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -62871,7 +62871,7 @@
       </c>
       <c r="S722" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -62956,7 +62956,7 @@
       </c>
       <c r="S723" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -63041,7 +63041,7 @@
       </c>
       <c r="S724" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -63126,7 +63126,7 @@
       </c>
       <c r="S725" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -63211,7 +63211,7 @@
       </c>
       <c r="S726" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -63296,7 +63296,7 @@
       </c>
       <c r="S727" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -63381,7 +63381,7 @@
       </c>
       <c r="S728" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -63466,7 +63466,7 @@
       </c>
       <c r="S729" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -63551,7 +63551,7 @@
       </c>
       <c r="S730" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -63636,7 +63636,7 @@
       </c>
       <c r="S731" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -63721,7 +63721,7 @@
       </c>
       <c r="S732" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -63806,7 +63806,7 @@
       </c>
       <c r="S733" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -63891,7 +63891,7 @@
       </c>
       <c r="S734" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -63976,7 +63976,7 @@
       </c>
       <c r="S735" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -64061,7 +64061,7 @@
       </c>
       <c r="S736" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -64146,7 +64146,7 @@
       </c>
       <c r="S737" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -64231,7 +64231,7 @@
       </c>
       <c r="S738" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -64316,7 +64316,7 @@
       </c>
       <c r="S739" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -64401,7 +64401,7 @@
       </c>
       <c r="S740" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -64486,7 +64486,7 @@
       </c>
       <c r="S741" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -64571,7 +64571,7 @@
       </c>
       <c r="S742" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -64660,7 +64660,7 @@
       </c>
       <c r="S743" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -64749,7 +64749,7 @@
       </c>
       <c r="S744" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -64838,7 +64838,7 @@
       </c>
       <c r="S745" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -64927,7 +64927,7 @@
       </c>
       <c r="S746" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -65016,7 +65016,7 @@
       </c>
       <c r="S747" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -65105,7 +65105,7 @@
       </c>
       <c r="S748" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -65194,7 +65194,7 @@
       </c>
       <c r="S749" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -65283,7 +65283,7 @@
       </c>
       <c r="S750" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -65372,7 +65372,7 @@
       </c>
       <c r="S751" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -65461,7 +65461,7 @@
       </c>
       <c r="S752" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -65550,7 +65550,7 @@
       </c>
       <c r="S753" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -65639,7 +65639,7 @@
       </c>
       <c r="S754" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -65728,7 +65728,7 @@
       </c>
       <c r="S755" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -65817,7 +65817,7 @@
       </c>
       <c r="S756" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -65906,7 +65906,7 @@
       </c>
       <c r="S757" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -65995,7 +65995,7 @@
       </c>
       <c r="S758" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -66084,7 +66084,7 @@
       </c>
       <c r="S759" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -66173,7 +66173,7 @@
       </c>
       <c r="S760" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -66262,7 +66262,7 @@
       </c>
       <c r="S761" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -66351,7 +66351,7 @@
       </c>
       <c r="S762" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -66436,7 +66436,7 @@
       </c>
       <c r="S763" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -66521,7 +66521,7 @@
       </c>
       <c r="S764" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -66606,7 +66606,7 @@
       </c>
       <c r="S765" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -66691,7 +66691,7 @@
       </c>
       <c r="S766" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -66776,7 +66776,7 @@
       </c>
       <c r="S767" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -66861,7 +66861,7 @@
       </c>
       <c r="S768" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -66946,7 +66946,7 @@
       </c>
       <c r="S769" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -67031,7 +67031,7 @@
       </c>
       <c r="S770" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -67116,7 +67116,7 @@
       </c>
       <c r="S771" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -67201,7 +67201,7 @@
       </c>
       <c r="S772" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -67286,7 +67286,7 @@
       </c>
       <c r="S773" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -67375,7 +67375,7 @@
       </c>
       <c r="S774" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -67464,7 +67464,7 @@
       </c>
       <c r="S775" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -67553,7 +67553,7 @@
       </c>
       <c r="S776" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -67642,7 +67642,7 @@
       </c>
       <c r="S777" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -67731,7 +67731,7 @@
       </c>
       <c r="S778" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -67820,7 +67820,7 @@
       </c>
       <c r="S779" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -67909,7 +67909,7 @@
       </c>
       <c r="S780" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -67998,7 +67998,7 @@
       </c>
       <c r="S781" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -68087,7 +68087,7 @@
       </c>
       <c r="S782" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -68176,7 +68176,7 @@
       </c>
       <c r="S783" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -68261,7 +68261,7 @@
       </c>
       <c r="S784" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -68346,7 +68346,7 @@
       </c>
       <c r="S785" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -68431,7 +68431,7 @@
       </c>
       <c r="S786" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -68516,7 +68516,7 @@
       </c>
       <c r="S787" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -68601,7 +68601,7 @@
       </c>
       <c r="S788" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -68686,7 +68686,7 @@
       </c>
       <c r="S789" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -68771,7 +68771,7 @@
       </c>
       <c r="S790" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -68856,7 +68856,7 @@
       </c>
       <c r="S791" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -68941,7 +68941,7 @@
       </c>
       <c r="S792" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -69026,7 +69026,7 @@
       </c>
       <c r="S793" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -69111,7 +69111,7 @@
       </c>
       <c r="S794" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -69200,7 +69200,7 @@
       </c>
       <c r="S795" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -69289,7 +69289,7 @@
       </c>
       <c r="S796" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -69378,7 +69378,7 @@
       </c>
       <c r="S797" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -69467,7 +69467,7 @@
       </c>
       <c r="S798" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -69556,7 +69556,7 @@
       </c>
       <c r="S799" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -69645,7 +69645,7 @@
       </c>
       <c r="S800" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -69734,7 +69734,7 @@
       </c>
       <c r="S801" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -69823,7 +69823,7 @@
       </c>
       <c r="S802" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -69912,7 +69912,7 @@
       </c>
       <c r="S803" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -70001,7 +70001,7 @@
       </c>
       <c r="S804" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -70086,7 +70086,7 @@
       </c>
       <c r="S805" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -70171,7 +70171,7 @@
       </c>
       <c r="S806" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -70256,7 +70256,7 @@
       </c>
       <c r="S807" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -70341,7 +70341,7 @@
       </c>
       <c r="S808" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -70426,7 +70426,7 @@
       </c>
       <c r="S809" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -70511,7 +70511,7 @@
       </c>
       <c r="S810" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -70596,7 +70596,7 @@
       </c>
       <c r="S811" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -70681,7 +70681,7 @@
       </c>
       <c r="S812" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -70766,7 +70766,7 @@
       </c>
       <c r="S813" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -70851,7 +70851,7 @@
       </c>
       <c r="S814" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -70936,7 +70936,7 @@
       </c>
       <c r="S815" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -71021,7 +71021,7 @@
       </c>
       <c r="S816" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -71106,7 +71106,7 @@
       </c>
       <c r="S817" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -71191,7 +71191,7 @@
       </c>
       <c r="S818" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -71276,7 +71276,7 @@
       </c>
       <c r="S819" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -71361,7 +71361,7 @@
       </c>
       <c r="S820" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -71446,7 +71446,7 @@
       </c>
       <c r="S821" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -71531,7 +71531,7 @@
       </c>
       <c r="S822" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -71616,7 +71616,7 @@
       </c>
       <c r="S823" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -71701,7 +71701,7 @@
       </c>
       <c r="S824" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -71786,7 +71786,7 @@
       </c>
       <c r="S825" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -71871,7 +71871,7 @@
       </c>
       <c r="S826" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -71960,7 +71960,7 @@
       </c>
       <c r="S827" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -72049,7 +72049,7 @@
       </c>
       <c r="S828" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -72138,7 +72138,7 @@
       </c>
       <c r="S829" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -72227,7 +72227,7 @@
       </c>
       <c r="S830" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -72316,7 +72316,7 @@
       </c>
       <c r="S831" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -72405,7 +72405,7 @@
       </c>
       <c r="S832" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -72494,7 +72494,7 @@
       </c>
       <c r="S833" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -72583,7 +72583,7 @@
       </c>
       <c r="S834" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -72672,7 +72672,7 @@
       </c>
       <c r="S835" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -72761,7 +72761,7 @@
       </c>
       <c r="S836" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -72850,7 +72850,7 @@
       </c>
       <c r="S837" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -72939,7 +72939,7 @@
       </c>
       <c r="S838" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -73028,7 +73028,7 @@
       </c>
       <c r="S839" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -73117,7 +73117,7 @@
       </c>
       <c r="S840" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -73206,7 +73206,7 @@
       </c>
       <c r="S841" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -73295,7 +73295,7 @@
       </c>
       <c r="S842" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -73384,7 +73384,7 @@
       </c>
       <c r="S843" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -73473,7 +73473,7 @@
       </c>
       <c r="S844" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -73562,7 +73562,7 @@
       </c>
       <c r="S845" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -73651,7 +73651,7 @@
       </c>
       <c r="S846" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -73736,7 +73736,7 @@
       </c>
       <c r="S847" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -73821,7 +73821,7 @@
       </c>
       <c r="S848" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -73906,7 +73906,7 @@
       </c>
       <c r="S849" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -73991,7 +73991,7 @@
       </c>
       <c r="S850" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -74076,7 +74076,7 @@
       </c>
       <c r="S851" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -74161,7 +74161,7 @@
       </c>
       <c r="S852" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -74246,7 +74246,7 @@
       </c>
       <c r="S853" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -74331,7 +74331,7 @@
       </c>
       <c r="S854" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -74416,7 +74416,7 @@
       </c>
       <c r="S855" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -74501,7 +74501,7 @@
       </c>
       <c r="S856" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -74586,7 +74586,7 @@
       </c>
       <c r="S857" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -74671,7 +74671,7 @@
       </c>
       <c r="S858" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -74756,7 +74756,7 @@
       </c>
       <c r="S859" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -74841,7 +74841,7 @@
       </c>
       <c r="S860" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -74926,7 +74926,7 @@
       </c>
       <c r="S861" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -75011,7 +75011,7 @@
       </c>
       <c r="S862" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -75096,7 +75096,7 @@
       </c>
       <c r="S863" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -75181,7 +75181,7 @@
       </c>
       <c r="S864" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -75266,7 +75266,7 @@
       </c>
       <c r="S865" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -75351,7 +75351,7 @@
       </c>
       <c r="S866" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -75436,7 +75436,7 @@
       </c>
       <c r="S867" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -75521,7 +75521,7 @@
       </c>
       <c r="S868" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -75610,7 +75610,7 @@
       </c>
       <c r="S869" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -75699,7 +75699,7 @@
       </c>
       <c r="S870" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -75788,7 +75788,7 @@
       </c>
       <c r="S871" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -75877,7 +75877,7 @@
       </c>
       <c r="S872" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -75966,7 +75966,7 @@
       </c>
       <c r="S873" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -76055,7 +76055,7 @@
       </c>
       <c r="S874" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -76144,7 +76144,7 @@
       </c>
       <c r="S875" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -76233,7 +76233,7 @@
       </c>
       <c r="S876" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -76322,7 +76322,7 @@
       </c>
       <c r="S877" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -76411,7 +76411,7 @@
       </c>
       <c r="S878" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -76500,7 +76500,7 @@
       </c>
       <c r="S879" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -76589,7 +76589,7 @@
       </c>
       <c r="S880" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -76678,7 +76678,7 @@
       </c>
       <c r="S881" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -76767,7 +76767,7 @@
       </c>
       <c r="S882" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -76856,7 +76856,7 @@
       </c>
       <c r="S883" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -76945,7 +76945,7 @@
       </c>
       <c r="S884" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -77034,7 +77034,7 @@
       </c>
       <c r="S885" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -77123,7 +77123,7 @@
       </c>
       <c r="S886" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -77212,7 +77212,7 @@
       </c>
       <c r="S887" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -77301,7 +77301,7 @@
       </c>
       <c r="S888" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -77433,7 +77433,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -77513,7 +77513,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-07-25T21:23:58Z"}</t>
+          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-07-26T21:25:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12625,7 +12625,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -13936,7 +13936,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14446,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -15041,7 +15041,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15296,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16008,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -17161,7 +17161,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -17416,7 +17416,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -17501,7 +17501,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17586,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17671,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -17841,7 +17841,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -18100,7 +18100,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -18367,7 +18367,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -18812,7 +18812,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -19326,7 +19326,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -20176,7 +20176,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -20261,7 +20261,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -20686,7 +20686,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -20941,7 +20941,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -21026,7 +21026,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -21281,7 +21281,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -21536,7 +21536,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -21706,7 +21706,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -21795,7 +21795,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -22062,7 +22062,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -22151,7 +22151,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -22240,7 +22240,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -22507,7 +22507,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22596,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -22685,7 +22685,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -22774,7 +22774,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -22952,7 +22952,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -23041,7 +23041,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -23130,7 +23130,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -23308,7 +23308,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -23397,7 +23397,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -23486,7 +23486,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -23575,7 +23575,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -23753,7 +23753,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24198,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -24287,7 +24287,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -24376,7 +24376,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -24461,7 +24461,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -24716,7 +24716,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -24886,7 +24886,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -24971,7 +24971,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25056,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -25226,7 +25226,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25396,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -25566,7 +25566,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -25736,7 +25736,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -25906,7 +25906,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -26076,7 +26076,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -26161,7 +26161,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -26335,7 +26335,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -26424,7 +26424,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -26602,7 +26602,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -26780,7 +26780,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -26869,7 +26869,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -26958,7 +26958,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -27225,7 +27225,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -27403,7 +27403,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -27492,7 +27492,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -27670,7 +27670,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -27759,7 +27759,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -27848,7 +27848,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -27937,7 +27937,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -28026,7 +28026,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -28196,7 +28196,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28281,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -28366,7 +28366,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -28451,7 +28451,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -28876,7 +28876,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -29046,7 +29046,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -29216,7 +29216,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -29301,7 +29301,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -29386,7 +29386,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -29471,7 +29471,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -29556,7 +29556,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -29641,7 +29641,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -29726,7 +29726,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -29811,7 +29811,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -29985,7 +29985,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -30341,7 +30341,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -30430,7 +30430,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -30608,7 +30608,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -31231,7 +31231,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -31498,7 +31498,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -31587,7 +31587,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -31676,7 +31676,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -31761,7 +31761,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -31846,7 +31846,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -31931,7 +31931,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -32101,7 +32101,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -32186,7 +32186,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -32271,7 +32271,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -32356,7 +32356,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -32441,7 +32441,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -32526,7 +32526,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -32611,7 +32611,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -32696,7 +32696,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -32951,7 +32951,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -33036,7 +33036,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -33291,7 +33291,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -33376,7 +33376,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -33461,7 +33461,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -33724,7 +33724,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -33813,7 +33813,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -33902,7 +33902,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -33991,7 +33991,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -34080,7 +34080,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -34169,7 +34169,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -34258,7 +34258,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -34347,7 +34347,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -34436,7 +34436,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -34525,7 +34525,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -34614,7 +34614,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -34703,7 +34703,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -34881,7 +34881,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -35148,7 +35148,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -35237,7 +35237,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -35326,7 +35326,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -35411,7 +35411,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -35496,7 +35496,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -35581,7 +35581,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -35836,7 +35836,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -36006,7 +36006,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -36091,7 +36091,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -36176,7 +36176,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -36261,7 +36261,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -36350,7 +36350,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -36439,7 +36439,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -36706,7 +36706,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -36795,7 +36795,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -36884,7 +36884,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -36973,7 +36973,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -37062,7 +37062,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -37151,7 +37151,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -37236,7 +37236,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -37321,7 +37321,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -37491,7 +37491,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -37576,7 +37576,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -37661,7 +37661,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -37746,7 +37746,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -37831,7 +37831,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -38001,7 +38001,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -38086,7 +38086,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -38256,7 +38256,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -38341,7 +38341,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -38426,7 +38426,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -38511,7 +38511,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -38596,7 +38596,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38681,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -38766,7 +38766,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -38851,7 +38851,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -38936,7 +38936,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -39021,7 +39021,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -39110,7 +39110,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -39199,7 +39199,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -39288,7 +39288,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -39377,7 +39377,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -39466,7 +39466,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -39644,7 +39644,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -39822,7 +39822,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -39911,7 +39911,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -40000,7 +40000,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -40089,7 +40089,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -40178,7 +40178,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -40267,7 +40267,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -40445,7 +40445,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -40534,7 +40534,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -40623,7 +40623,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -40712,7 +40712,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -40886,7 +40886,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -40971,7 +40971,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -41141,7 +41141,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -41226,7 +41226,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -41311,7 +41311,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -41396,7 +41396,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -41481,7 +41481,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -41566,7 +41566,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -41651,7 +41651,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -41736,7 +41736,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -41825,7 +41825,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -41914,7 +41914,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -42003,7 +42003,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -42092,7 +42092,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -42181,7 +42181,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -42270,7 +42270,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -42359,7 +42359,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -42448,7 +42448,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -42537,7 +42537,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -42626,7 +42626,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -42711,7 +42711,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -42796,7 +42796,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -42881,7 +42881,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -43051,7 +43051,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -43221,7 +43221,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -43306,7 +43306,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -43391,7 +43391,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -43476,7 +43476,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -43561,7 +43561,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -43646,7 +43646,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -43731,7 +43731,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -43816,7 +43816,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -43901,7 +43901,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -43986,7 +43986,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -44071,7 +44071,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -44156,7 +44156,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -44241,7 +44241,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -44411,7 +44411,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -44496,7 +44496,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -44585,7 +44585,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -44674,7 +44674,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -44763,7 +44763,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -44852,7 +44852,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -44941,7 +44941,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -45030,7 +45030,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -45119,7 +45119,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -45208,7 +45208,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -45297,7 +45297,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -45386,7 +45386,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -45475,7 +45475,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -45564,7 +45564,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -45653,7 +45653,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -45742,7 +45742,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -45831,7 +45831,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -45920,7 +45920,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -46009,7 +46009,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -46098,7 +46098,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -46187,7 +46187,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -46276,7 +46276,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -46361,7 +46361,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -46446,7 +46446,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -46531,7 +46531,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -46616,7 +46616,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -46701,7 +46701,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -46786,7 +46786,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -46871,7 +46871,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -46956,7 +46956,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -47041,7 +47041,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -47126,7 +47126,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -47211,7 +47211,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -47300,7 +47300,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -47389,7 +47389,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -47478,7 +47478,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -47567,7 +47567,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -47656,7 +47656,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -47745,7 +47745,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -47834,7 +47834,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -47923,7 +47923,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -48012,7 +48012,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -48101,7 +48101,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -48186,7 +48186,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -48271,7 +48271,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -48356,7 +48356,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -48441,7 +48441,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -48526,7 +48526,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -48696,7 +48696,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -48781,7 +48781,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -48866,7 +48866,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -48951,7 +48951,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -49036,7 +49036,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -49125,7 +49125,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -49214,7 +49214,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -49303,7 +49303,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -49392,7 +49392,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -49481,7 +49481,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -49570,7 +49570,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -49659,7 +49659,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -49748,7 +49748,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -49837,7 +49837,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -49926,7 +49926,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -50011,7 +50011,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -50096,7 +50096,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -50181,7 +50181,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -50266,7 +50266,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -50436,7 +50436,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -50521,7 +50521,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -50606,7 +50606,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -50691,7 +50691,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -50776,7 +50776,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -50861,7 +50861,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -50946,7 +50946,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -51031,7 +51031,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -51116,7 +51116,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -51201,7 +51201,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -51286,7 +51286,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -51371,7 +51371,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -51456,7 +51456,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -51541,7 +51541,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -51626,7 +51626,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -51711,7 +51711,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -51796,7 +51796,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -51885,7 +51885,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -51974,7 +51974,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -52063,7 +52063,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -52152,7 +52152,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -52241,7 +52241,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -52330,7 +52330,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -52419,7 +52419,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -52508,7 +52508,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -52597,7 +52597,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -52686,7 +52686,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -52775,7 +52775,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -52864,7 +52864,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -52953,7 +52953,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -53042,7 +53042,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -53131,7 +53131,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -53220,7 +53220,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -53309,7 +53309,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -53398,7 +53398,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -53487,7 +53487,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -53576,7 +53576,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -53661,7 +53661,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -53746,7 +53746,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -53831,7 +53831,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -53916,7 +53916,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -54001,7 +54001,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -54086,7 +54086,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -54171,7 +54171,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -54256,7 +54256,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -54426,7 +54426,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -54511,7 +54511,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -54596,7 +54596,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -54681,7 +54681,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -54766,7 +54766,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -54851,7 +54851,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -54936,7 +54936,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -55021,7 +55021,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -55106,7 +55106,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -55191,7 +55191,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -55276,7 +55276,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -55361,7 +55361,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -55446,7 +55446,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -55531,7 +55531,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -55616,7 +55616,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -55701,7 +55701,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -55786,7 +55786,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -55871,7 +55871,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -55956,7 +55956,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -56041,7 +56041,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -56126,7 +56126,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -56211,7 +56211,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -56296,7 +56296,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -56381,7 +56381,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -56466,7 +56466,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -56551,7 +56551,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -56636,7 +56636,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -56721,7 +56721,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56806,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -56891,7 +56891,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -56976,7 +56976,7 @@
       </c>
       <c r="S655" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -57061,7 +57061,7 @@
       </c>
       <c r="S656" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -57146,7 +57146,7 @@
       </c>
       <c r="S657" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -57231,7 +57231,7 @@
       </c>
       <c r="S658" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -57316,7 +57316,7 @@
       </c>
       <c r="S659" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -57401,7 +57401,7 @@
       </c>
       <c r="S660" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -57486,7 +57486,7 @@
       </c>
       <c r="S661" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -57571,7 +57571,7 @@
       </c>
       <c r="S662" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -57656,7 +57656,7 @@
       </c>
       <c r="S663" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -57741,7 +57741,7 @@
       </c>
       <c r="S664" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -57826,7 +57826,7 @@
       </c>
       <c r="S665" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -57911,7 +57911,7 @@
       </c>
       <c r="S666" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -57996,7 +57996,7 @@
       </c>
       <c r="S667" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -58081,7 +58081,7 @@
       </c>
       <c r="S668" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -58166,7 +58166,7 @@
       </c>
       <c r="S669" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -58251,7 +58251,7 @@
       </c>
       <c r="S670" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -58340,7 +58340,7 @@
       </c>
       <c r="S671" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -58429,7 +58429,7 @@
       </c>
       <c r="S672" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -58518,7 +58518,7 @@
       </c>
       <c r="S673" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -58607,7 +58607,7 @@
       </c>
       <c r="S674" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -58696,7 +58696,7 @@
       </c>
       <c r="S675" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -58785,7 +58785,7 @@
       </c>
       <c r="S676" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -58874,7 +58874,7 @@
       </c>
       <c r="S677" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -58963,7 +58963,7 @@
       </c>
       <c r="S678" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -59052,7 +59052,7 @@
       </c>
       <c r="S679" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -59141,7 +59141,7 @@
       </c>
       <c r="S680" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -59230,7 +59230,7 @@
       </c>
       <c r="S681" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -59319,7 +59319,7 @@
       </c>
       <c r="S682" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -59408,7 +59408,7 @@
       </c>
       <c r="S683" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -59497,7 +59497,7 @@
       </c>
       <c r="S684" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -59586,7 +59586,7 @@
       </c>
       <c r="S685" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -59675,7 +59675,7 @@
       </c>
       <c r="S686" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -59764,7 +59764,7 @@
       </c>
       <c r="S687" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -59853,7 +59853,7 @@
       </c>
       <c r="S688" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -59942,7 +59942,7 @@
       </c>
       <c r="S689" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -60031,7 +60031,7 @@
       </c>
       <c r="S690" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -60120,7 +60120,7 @@
       </c>
       <c r="S691" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -60209,7 +60209,7 @@
       </c>
       <c r="S692" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="S693" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -60387,7 +60387,7 @@
       </c>
       <c r="S694" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -60476,7 +60476,7 @@
       </c>
       <c r="S695" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -60565,7 +60565,7 @@
       </c>
       <c r="S696" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -60654,7 +60654,7 @@
       </c>
       <c r="S697" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -60743,7 +60743,7 @@
       </c>
       <c r="S698" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -60832,7 +60832,7 @@
       </c>
       <c r="S699" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -60921,7 +60921,7 @@
       </c>
       <c r="S700" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -61010,7 +61010,7 @@
       </c>
       <c r="S701" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -61099,7 +61099,7 @@
       </c>
       <c r="S702" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -61188,7 +61188,7 @@
       </c>
       <c r="S703" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -61277,7 +61277,7 @@
       </c>
       <c r="S704" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -61366,7 +61366,7 @@
       </c>
       <c r="S705" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -61455,7 +61455,7 @@
       </c>
       <c r="S706" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -61544,7 +61544,7 @@
       </c>
       <c r="S707" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -61633,7 +61633,7 @@
       </c>
       <c r="S708" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -61722,7 +61722,7 @@
       </c>
       <c r="S709" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -61811,7 +61811,7 @@
       </c>
       <c r="S710" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -61900,7 +61900,7 @@
       </c>
       <c r="S711" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -61989,7 +61989,7 @@
       </c>
       <c r="S712" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -62078,7 +62078,7 @@
       </c>
       <c r="S713" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -62167,7 +62167,7 @@
       </c>
       <c r="S714" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -62256,7 +62256,7 @@
       </c>
       <c r="S715" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -62345,7 +62345,7 @@
       </c>
       <c r="S716" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -62434,7 +62434,7 @@
       </c>
       <c r="S717" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -62523,7 +62523,7 @@
       </c>
       <c r="S718" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -62612,7 +62612,7 @@
       </c>
       <c r="S719" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -62701,7 +62701,7 @@
       </c>
       <c r="S720" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -62786,7 +62786,7 @@
       </c>
       <c r="S721" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -62871,7 +62871,7 @@
       </c>
       <c r="S722" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -62956,7 +62956,7 @@
       </c>
       <c r="S723" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -63041,7 +63041,7 @@
       </c>
       <c r="S724" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -63126,7 +63126,7 @@
       </c>
       <c r="S725" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -63211,7 +63211,7 @@
       </c>
       <c r="S726" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -63296,7 +63296,7 @@
       </c>
       <c r="S727" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -63381,7 +63381,7 @@
       </c>
       <c r="S728" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -63466,7 +63466,7 @@
       </c>
       <c r="S729" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -63551,7 +63551,7 @@
       </c>
       <c r="S730" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -63636,7 +63636,7 @@
       </c>
       <c r="S731" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -63721,7 +63721,7 @@
       </c>
       <c r="S732" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -63806,7 +63806,7 @@
       </c>
       <c r="S733" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -63891,7 +63891,7 @@
       </c>
       <c r="S734" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -63976,7 +63976,7 @@
       </c>
       <c r="S735" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -64061,7 +64061,7 @@
       </c>
       <c r="S736" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -64146,7 +64146,7 @@
       </c>
       <c r="S737" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -64231,7 +64231,7 @@
       </c>
       <c r="S738" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -64316,7 +64316,7 @@
       </c>
       <c r="S739" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -64401,7 +64401,7 @@
       </c>
       <c r="S740" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -64486,7 +64486,7 @@
       </c>
       <c r="S741" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -64571,7 +64571,7 @@
       </c>
       <c r="S742" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -64660,7 +64660,7 @@
       </c>
       <c r="S743" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -64749,7 +64749,7 @@
       </c>
       <c r="S744" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -64838,7 +64838,7 @@
       </c>
       <c r="S745" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -64927,7 +64927,7 @@
       </c>
       <c r="S746" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -65016,7 +65016,7 @@
       </c>
       <c r="S747" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -65105,7 +65105,7 @@
       </c>
       <c r="S748" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -65194,7 +65194,7 @@
       </c>
       <c r="S749" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -65283,7 +65283,7 @@
       </c>
       <c r="S750" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -65372,7 +65372,7 @@
       </c>
       <c r="S751" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -65461,7 +65461,7 @@
       </c>
       <c r="S752" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -65550,7 +65550,7 @@
       </c>
       <c r="S753" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -65639,7 +65639,7 @@
       </c>
       <c r="S754" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -65728,7 +65728,7 @@
       </c>
       <c r="S755" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -65817,7 +65817,7 @@
       </c>
       <c r="S756" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -65906,7 +65906,7 @@
       </c>
       <c r="S757" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -65995,7 +65995,7 @@
       </c>
       <c r="S758" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -66084,7 +66084,7 @@
       </c>
       <c r="S759" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -66173,7 +66173,7 @@
       </c>
       <c r="S760" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -66262,7 +66262,7 @@
       </c>
       <c r="S761" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -66351,7 +66351,7 @@
       </c>
       <c r="S762" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -66436,7 +66436,7 @@
       </c>
       <c r="S763" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -66521,7 +66521,7 @@
       </c>
       <c r="S764" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -66606,7 +66606,7 @@
       </c>
       <c r="S765" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -66691,7 +66691,7 @@
       </c>
       <c r="S766" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -66776,7 +66776,7 @@
       </c>
       <c r="S767" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -66861,7 +66861,7 @@
       </c>
       <c r="S768" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -66946,7 +66946,7 @@
       </c>
       <c r="S769" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -67031,7 +67031,7 @@
       </c>
       <c r="S770" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -67116,7 +67116,7 @@
       </c>
       <c r="S771" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -67201,7 +67201,7 @@
       </c>
       <c r="S772" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -67286,7 +67286,7 @@
       </c>
       <c r="S773" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -67375,7 +67375,7 @@
       </c>
       <c r="S774" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -67464,7 +67464,7 @@
       </c>
       <c r="S775" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -67553,7 +67553,7 @@
       </c>
       <c r="S776" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -67642,7 +67642,7 @@
       </c>
       <c r="S777" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -67731,7 +67731,7 @@
       </c>
       <c r="S778" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -67820,7 +67820,7 @@
       </c>
       <c r="S779" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -67909,7 +67909,7 @@
       </c>
       <c r="S780" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -67998,7 +67998,7 @@
       </c>
       <c r="S781" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -68087,7 +68087,7 @@
       </c>
       <c r="S782" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -68176,7 +68176,7 @@
       </c>
       <c r="S783" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -68261,7 +68261,7 @@
       </c>
       <c r="S784" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -68346,7 +68346,7 @@
       </c>
       <c r="S785" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -68431,7 +68431,7 @@
       </c>
       <c r="S786" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -68516,7 +68516,7 @@
       </c>
       <c r="S787" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -68601,7 +68601,7 @@
       </c>
       <c r="S788" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -68686,7 +68686,7 @@
       </c>
       <c r="S789" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -68771,7 +68771,7 @@
       </c>
       <c r="S790" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -68856,7 +68856,7 @@
       </c>
       <c r="S791" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -68941,7 +68941,7 @@
       </c>
       <c r="S792" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -69026,7 +69026,7 @@
       </c>
       <c r="S793" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -69111,7 +69111,7 @@
       </c>
       <c r="S794" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -69200,7 +69200,7 @@
       </c>
       <c r="S795" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -69289,7 +69289,7 @@
       </c>
       <c r="S796" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -69378,7 +69378,7 @@
       </c>
       <c r="S797" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -69467,7 +69467,7 @@
       </c>
       <c r="S798" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -69556,7 +69556,7 @@
       </c>
       <c r="S799" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -69645,7 +69645,7 @@
       </c>
       <c r="S800" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -69734,7 +69734,7 @@
       </c>
       <c r="S801" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -69823,7 +69823,7 @@
       </c>
       <c r="S802" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -69912,7 +69912,7 @@
       </c>
       <c r="S803" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -70001,7 +70001,7 @@
       </c>
       <c r="S804" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -70086,7 +70086,7 @@
       </c>
       <c r="S805" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -70171,7 +70171,7 @@
       </c>
       <c r="S806" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -70256,7 +70256,7 @@
       </c>
       <c r="S807" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -70341,7 +70341,7 @@
       </c>
       <c r="S808" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -70426,7 +70426,7 @@
       </c>
       <c r="S809" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -70511,7 +70511,7 @@
       </c>
       <c r="S810" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -70596,7 +70596,7 @@
       </c>
       <c r="S811" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -70681,7 +70681,7 @@
       </c>
       <c r="S812" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -70766,7 +70766,7 @@
       </c>
       <c r="S813" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -70851,7 +70851,7 @@
       </c>
       <c r="S814" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -70936,7 +70936,7 @@
       </c>
       <c r="S815" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -71021,7 +71021,7 @@
       </c>
       <c r="S816" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -71106,7 +71106,7 @@
       </c>
       <c r="S817" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -71191,7 +71191,7 @@
       </c>
       <c r="S818" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -71276,7 +71276,7 @@
       </c>
       <c r="S819" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -71361,7 +71361,7 @@
       </c>
       <c r="S820" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -71446,7 +71446,7 @@
       </c>
       <c r="S821" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -71531,7 +71531,7 @@
       </c>
       <c r="S822" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -71616,7 +71616,7 @@
       </c>
       <c r="S823" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -71701,7 +71701,7 @@
       </c>
       <c r="S824" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -71786,7 +71786,7 @@
       </c>
       <c r="S825" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -71871,7 +71871,7 @@
       </c>
       <c r="S826" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -71960,7 +71960,7 @@
       </c>
       <c r="S827" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -72049,7 +72049,7 @@
       </c>
       <c r="S828" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -72138,7 +72138,7 @@
       </c>
       <c r="S829" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -72227,7 +72227,7 @@
       </c>
       <c r="S830" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -72316,7 +72316,7 @@
       </c>
       <c r="S831" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -72405,7 +72405,7 @@
       </c>
       <c r="S832" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -72494,7 +72494,7 @@
       </c>
       <c r="S833" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -72583,7 +72583,7 @@
       </c>
       <c r="S834" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -72672,7 +72672,7 @@
       </c>
       <c r="S835" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -72761,7 +72761,7 @@
       </c>
       <c r="S836" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -72850,7 +72850,7 @@
       </c>
       <c r="S837" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -72939,7 +72939,7 @@
       </c>
       <c r="S838" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -73028,7 +73028,7 @@
       </c>
       <c r="S839" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -73117,7 +73117,7 @@
       </c>
       <c r="S840" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -73206,7 +73206,7 @@
       </c>
       <c r="S841" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -73295,7 +73295,7 @@
       </c>
       <c r="S842" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -73384,7 +73384,7 @@
       </c>
       <c r="S843" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -73473,7 +73473,7 @@
       </c>
       <c r="S844" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -73562,7 +73562,7 @@
       </c>
       <c r="S845" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -73651,7 +73651,7 @@
       </c>
       <c r="S846" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -73736,7 +73736,7 @@
       </c>
       <c r="S847" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -73821,7 +73821,7 @@
       </c>
       <c r="S848" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -73906,7 +73906,7 @@
       </c>
       <c r="S849" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -73991,7 +73991,7 @@
       </c>
       <c r="S850" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -74076,7 +74076,7 @@
       </c>
       <c r="S851" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -74161,7 +74161,7 @@
       </c>
       <c r="S852" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -74246,7 +74246,7 @@
       </c>
       <c r="S853" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -74331,7 +74331,7 @@
       </c>
       <c r="S854" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -74416,7 +74416,7 @@
       </c>
       <c r="S855" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -74501,7 +74501,7 @@
       </c>
       <c r="S856" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -74586,7 +74586,7 @@
       </c>
       <c r="S857" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -74671,7 +74671,7 @@
       </c>
       <c r="S858" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -74756,7 +74756,7 @@
       </c>
       <c r="S859" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -74841,7 +74841,7 @@
       </c>
       <c r="S860" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -74926,7 +74926,7 @@
       </c>
       <c r="S861" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -75011,7 +75011,7 @@
       </c>
       <c r="S862" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -75096,7 +75096,7 @@
       </c>
       <c r="S863" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -75181,7 +75181,7 @@
       </c>
       <c r="S864" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -75266,7 +75266,7 @@
       </c>
       <c r="S865" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -75351,7 +75351,7 @@
       </c>
       <c r="S866" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -75436,7 +75436,7 @@
       </c>
       <c r="S867" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -75521,7 +75521,7 @@
       </c>
       <c r="S868" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -75610,7 +75610,7 @@
       </c>
       <c r="S869" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -75699,7 +75699,7 @@
       </c>
       <c r="S870" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -75788,7 +75788,7 @@
       </c>
       <c r="S871" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -75877,7 +75877,7 @@
       </c>
       <c r="S872" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -75966,7 +75966,7 @@
       </c>
       <c r="S873" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -76055,7 +76055,7 @@
       </c>
       <c r="S874" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -76144,7 +76144,7 @@
       </c>
       <c r="S875" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -76233,7 +76233,7 @@
       </c>
       <c r="S876" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -76322,7 +76322,7 @@
       </c>
       <c r="S877" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -76411,7 +76411,7 @@
       </c>
       <c r="S878" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -76500,7 +76500,7 @@
       </c>
       <c r="S879" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -76589,7 +76589,7 @@
       </c>
       <c r="S880" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -76678,7 +76678,7 @@
       </c>
       <c r="S881" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -76767,7 +76767,7 @@
       </c>
       <c r="S882" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -76856,7 +76856,7 @@
       </c>
       <c r="S883" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -76945,7 +76945,7 @@
       </c>
       <c r="S884" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -77034,7 +77034,7 @@
       </c>
       <c r="S885" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -77123,7 +77123,7 @@
       </c>
       <c r="S886" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -77212,7 +77212,7 @@
       </c>
       <c r="S887" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -77301,7 +77301,7 @@
       </c>
       <c r="S888" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -77433,7 +77433,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:56Z</t>
+          <t>2026-08-07T14:18:55Z</t>
         </is>
       </c>
     </row>
@@ -77513,7 +77513,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-08-07T00:56:56Z"}</t>
+          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-08-07T14:18:55Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12625,7 +12625,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -13936,7 +13936,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14446,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -15041,7 +15041,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15296,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16008,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -17161,7 +17161,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -17416,7 +17416,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -17501,7 +17501,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17586,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17671,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -17841,7 +17841,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -18100,7 +18100,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -18367,7 +18367,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -18812,7 +18812,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -19326,7 +19326,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -20176,7 +20176,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -20261,7 +20261,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -20686,7 +20686,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -20941,7 +20941,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -21026,7 +21026,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -21281,7 +21281,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -21536,7 +21536,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -21706,7 +21706,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -21795,7 +21795,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -22062,7 +22062,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -22151,7 +22151,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -22240,7 +22240,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -22507,7 +22507,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22596,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -22685,7 +22685,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -22774,7 +22774,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -22952,7 +22952,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -23041,7 +23041,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -23130,7 +23130,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -23308,7 +23308,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -23397,7 +23397,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -23486,7 +23486,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -23575,7 +23575,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -23753,7 +23753,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24198,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -24287,7 +24287,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -24376,7 +24376,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -24461,7 +24461,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -24716,7 +24716,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -24886,7 +24886,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -24971,7 +24971,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25056,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -25226,7 +25226,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25396,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -25566,7 +25566,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -25736,7 +25736,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -25906,7 +25906,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -26076,7 +26076,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -26161,7 +26161,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -26335,7 +26335,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -26424,7 +26424,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -26602,7 +26602,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -26780,7 +26780,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -26869,7 +26869,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -26958,7 +26958,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -27225,7 +27225,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -27403,7 +27403,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -27492,7 +27492,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -27670,7 +27670,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -27759,7 +27759,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -27848,7 +27848,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -27937,7 +27937,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -28026,7 +28026,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -28196,7 +28196,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28281,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -28366,7 +28366,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -28451,7 +28451,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -28876,7 +28876,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -29046,7 +29046,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -29216,7 +29216,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -29301,7 +29301,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -29386,7 +29386,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -29471,7 +29471,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -29556,7 +29556,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -29641,7 +29641,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -29726,7 +29726,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -29811,7 +29811,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -29985,7 +29985,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -30341,7 +30341,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -30430,7 +30430,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -30608,7 +30608,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -31231,7 +31231,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -31498,7 +31498,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -31587,7 +31587,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -31676,7 +31676,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -31761,7 +31761,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -31846,7 +31846,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -31931,7 +31931,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -32101,7 +32101,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -32186,7 +32186,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -32271,7 +32271,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -32356,7 +32356,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -32441,7 +32441,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -32526,7 +32526,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -32611,7 +32611,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -32696,7 +32696,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -32951,7 +32951,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -33036,7 +33036,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -33291,7 +33291,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -33376,7 +33376,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -33461,7 +33461,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -33724,7 +33724,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -33813,7 +33813,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -33902,7 +33902,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -33991,7 +33991,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -34080,7 +34080,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -34169,7 +34169,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -34258,7 +34258,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -34347,7 +34347,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -34436,7 +34436,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -34525,7 +34525,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -34614,7 +34614,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -34703,7 +34703,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -34881,7 +34881,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -35148,7 +35148,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -35237,7 +35237,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -35326,7 +35326,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -35411,7 +35411,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -35496,7 +35496,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -35581,7 +35581,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -35836,7 +35836,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -36006,7 +36006,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -36091,7 +36091,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -36176,7 +36176,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -36261,7 +36261,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -36350,7 +36350,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -36439,7 +36439,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -36706,7 +36706,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -36795,7 +36795,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -36884,7 +36884,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -36973,7 +36973,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -37062,7 +37062,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -37151,7 +37151,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -37236,7 +37236,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -37321,7 +37321,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -37491,7 +37491,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -37576,7 +37576,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -37661,7 +37661,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -37746,7 +37746,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -37831,7 +37831,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -38001,7 +38001,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -38086,7 +38086,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -38256,7 +38256,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -38341,7 +38341,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -38426,7 +38426,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -38511,7 +38511,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -38596,7 +38596,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38681,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -38766,7 +38766,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -38851,7 +38851,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -38936,7 +38936,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -39021,7 +39021,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -39110,7 +39110,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -39199,7 +39199,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -39288,7 +39288,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -39377,7 +39377,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -39466,7 +39466,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -39644,7 +39644,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -39822,7 +39822,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -39911,7 +39911,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -40000,7 +40000,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -40089,7 +40089,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -40178,7 +40178,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -40267,7 +40267,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -40445,7 +40445,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -40534,7 +40534,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -40623,7 +40623,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -40712,7 +40712,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -40886,7 +40886,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -40971,7 +40971,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -41141,7 +41141,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -41226,7 +41226,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -41311,7 +41311,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -41396,7 +41396,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -41481,7 +41481,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -41566,7 +41566,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -41651,7 +41651,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -41736,7 +41736,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -41825,7 +41825,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -41914,7 +41914,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -42003,7 +42003,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -42092,7 +42092,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -42181,7 +42181,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -42270,7 +42270,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -42359,7 +42359,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -42448,7 +42448,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -42537,7 +42537,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -42626,7 +42626,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -42711,7 +42711,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -42796,7 +42796,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -42881,7 +42881,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -43051,7 +43051,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -43221,7 +43221,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -43306,7 +43306,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -43391,7 +43391,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -43476,7 +43476,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -43561,7 +43561,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -43646,7 +43646,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -43731,7 +43731,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -43816,7 +43816,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -43901,7 +43901,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -43986,7 +43986,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -44071,7 +44071,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -44156,7 +44156,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -44241,7 +44241,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -44411,7 +44411,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -44496,7 +44496,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -44585,7 +44585,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -44674,7 +44674,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -44763,7 +44763,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -44852,7 +44852,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -44941,7 +44941,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -45030,7 +45030,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -45119,7 +45119,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -45208,7 +45208,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -45297,7 +45297,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -45386,7 +45386,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -45475,7 +45475,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -45564,7 +45564,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -45653,7 +45653,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -45742,7 +45742,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -45831,7 +45831,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -45920,7 +45920,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -46009,7 +46009,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -46098,7 +46098,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -46187,7 +46187,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -46276,7 +46276,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -46361,7 +46361,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -46446,7 +46446,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -46531,7 +46531,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -46616,7 +46616,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -46701,7 +46701,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -46786,7 +46786,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -46871,7 +46871,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -46956,7 +46956,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -47041,7 +47041,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -47126,7 +47126,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -47211,7 +47211,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -47300,7 +47300,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -47389,7 +47389,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -47478,7 +47478,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -47567,7 +47567,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -47656,7 +47656,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -47745,7 +47745,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -47834,7 +47834,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -47923,7 +47923,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -48012,7 +48012,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -48101,7 +48101,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -48186,7 +48186,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -48271,7 +48271,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -48356,7 +48356,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -48441,7 +48441,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -48526,7 +48526,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -48696,7 +48696,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -48781,7 +48781,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -48866,7 +48866,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -48951,7 +48951,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -49036,7 +49036,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -49125,7 +49125,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -49214,7 +49214,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -49303,7 +49303,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -49392,7 +49392,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -49481,7 +49481,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -49570,7 +49570,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -49659,7 +49659,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -49748,7 +49748,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -49837,7 +49837,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -49926,7 +49926,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -50011,7 +50011,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -50096,7 +50096,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -50181,7 +50181,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -50266,7 +50266,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -50436,7 +50436,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -50521,7 +50521,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -50606,7 +50606,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -50691,7 +50691,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -50776,7 +50776,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -50861,7 +50861,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -50946,7 +50946,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -51031,7 +51031,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -51116,7 +51116,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -51201,7 +51201,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -51286,7 +51286,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -51371,7 +51371,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -51456,7 +51456,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -51541,7 +51541,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -51626,7 +51626,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -51711,7 +51711,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -51796,7 +51796,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -51885,7 +51885,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -51974,7 +51974,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -52063,7 +52063,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -52152,7 +52152,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -52241,7 +52241,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -52330,7 +52330,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -52419,7 +52419,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -52508,7 +52508,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -52597,7 +52597,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -52686,7 +52686,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -52775,7 +52775,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -52864,7 +52864,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -52953,7 +52953,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -53042,7 +53042,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -53131,7 +53131,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -53220,7 +53220,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -53309,7 +53309,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -53398,7 +53398,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -53487,7 +53487,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -53576,7 +53576,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -53661,7 +53661,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -53746,7 +53746,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -53831,7 +53831,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -53916,7 +53916,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -54001,7 +54001,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -54086,7 +54086,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -54171,7 +54171,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -54256,7 +54256,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -54426,7 +54426,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -54511,7 +54511,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -54596,7 +54596,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -54681,7 +54681,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -54766,7 +54766,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -54851,7 +54851,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -54936,7 +54936,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -55021,7 +55021,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -55106,7 +55106,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -55191,7 +55191,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -55276,7 +55276,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -55361,7 +55361,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -55446,7 +55446,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -55531,7 +55531,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -55616,7 +55616,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -55701,7 +55701,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -55786,7 +55786,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -55871,7 +55871,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -55956,7 +55956,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -56041,7 +56041,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -56126,7 +56126,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -56211,7 +56211,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -56296,7 +56296,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -56381,7 +56381,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -56466,7 +56466,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -56551,7 +56551,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -56636,7 +56636,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -56721,7 +56721,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56806,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -56891,7 +56891,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -56976,7 +56976,7 @@
       </c>
       <c r="S655" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -57061,7 +57061,7 @@
       </c>
       <c r="S656" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -57146,7 +57146,7 @@
       </c>
       <c r="S657" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -57231,7 +57231,7 @@
       </c>
       <c r="S658" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -57316,7 +57316,7 @@
       </c>
       <c r="S659" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -57401,7 +57401,7 @@
       </c>
       <c r="S660" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -57486,7 +57486,7 @@
       </c>
       <c r="S661" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -57571,7 +57571,7 @@
       </c>
       <c r="S662" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -57656,7 +57656,7 @@
       </c>
       <c r="S663" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -57741,7 +57741,7 @@
       </c>
       <c r="S664" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -57826,7 +57826,7 @@
       </c>
       <c r="S665" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -57911,7 +57911,7 @@
       </c>
       <c r="S666" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -57996,7 +57996,7 @@
       </c>
       <c r="S667" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -58081,7 +58081,7 @@
       </c>
       <c r="S668" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -58166,7 +58166,7 @@
       </c>
       <c r="S669" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -58251,7 +58251,7 @@
       </c>
       <c r="S670" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -58340,7 +58340,7 @@
       </c>
       <c r="S671" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -58429,7 +58429,7 @@
       </c>
       <c r="S672" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -58518,7 +58518,7 @@
       </c>
       <c r="S673" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -58607,7 +58607,7 @@
       </c>
       <c r="S674" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -58696,7 +58696,7 @@
       </c>
       <c r="S675" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -58785,7 +58785,7 @@
       </c>
       <c r="S676" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -58874,7 +58874,7 @@
       </c>
       <c r="S677" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -58963,7 +58963,7 @@
       </c>
       <c r="S678" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -59052,7 +59052,7 @@
       </c>
       <c r="S679" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -59141,7 +59141,7 @@
       </c>
       <c r="S680" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -59230,7 +59230,7 @@
       </c>
       <c r="S681" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -59319,7 +59319,7 @@
       </c>
       <c r="S682" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -59408,7 +59408,7 @@
       </c>
       <c r="S683" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -59497,7 +59497,7 @@
       </c>
       <c r="S684" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -59586,7 +59586,7 @@
       </c>
       <c r="S685" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -59675,7 +59675,7 @@
       </c>
       <c r="S686" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -59764,7 +59764,7 @@
       </c>
       <c r="S687" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -59853,7 +59853,7 @@
       </c>
       <c r="S688" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -59942,7 +59942,7 @@
       </c>
       <c r="S689" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -60031,7 +60031,7 @@
       </c>
       <c r="S690" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -60120,7 +60120,7 @@
       </c>
       <c r="S691" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -60209,7 +60209,7 @@
       </c>
       <c r="S692" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="S693" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -60387,7 +60387,7 @@
       </c>
       <c r="S694" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -60476,7 +60476,7 @@
       </c>
       <c r="S695" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -60565,7 +60565,7 @@
       </c>
       <c r="S696" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -60654,7 +60654,7 @@
       </c>
       <c r="S697" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -60743,7 +60743,7 @@
       </c>
       <c r="S698" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -60832,7 +60832,7 @@
       </c>
       <c r="S699" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -60921,7 +60921,7 @@
       </c>
       <c r="S700" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -61010,7 +61010,7 @@
       </c>
       <c r="S701" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -61099,7 +61099,7 @@
       </c>
       <c r="S702" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -61188,7 +61188,7 @@
       </c>
       <c r="S703" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -61277,7 +61277,7 @@
       </c>
       <c r="S704" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -61366,7 +61366,7 @@
       </c>
       <c r="S705" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -61455,7 +61455,7 @@
       </c>
       <c r="S706" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -61544,7 +61544,7 @@
       </c>
       <c r="S707" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -61633,7 +61633,7 @@
       </c>
       <c r="S708" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -61722,7 +61722,7 @@
       </c>
       <c r="S709" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -61811,7 +61811,7 @@
       </c>
       <c r="S710" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -61900,7 +61900,7 @@
       </c>
       <c r="S711" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -61989,7 +61989,7 @@
       </c>
       <c r="S712" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -62078,7 +62078,7 @@
       </c>
       <c r="S713" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -62167,7 +62167,7 @@
       </c>
       <c r="S714" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -62256,7 +62256,7 @@
       </c>
       <c r="S715" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -62345,7 +62345,7 @@
       </c>
       <c r="S716" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -62434,7 +62434,7 @@
       </c>
       <c r="S717" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -62523,7 +62523,7 @@
       </c>
       <c r="S718" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -62612,7 +62612,7 @@
       </c>
       <c r="S719" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -62701,7 +62701,7 @@
       </c>
       <c r="S720" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -62786,7 +62786,7 @@
       </c>
       <c r="S721" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -62871,7 +62871,7 @@
       </c>
       <c r="S722" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -62956,7 +62956,7 @@
       </c>
       <c r="S723" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -63041,7 +63041,7 @@
       </c>
       <c r="S724" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -63126,7 +63126,7 @@
       </c>
       <c r="S725" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -63211,7 +63211,7 @@
       </c>
       <c r="S726" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -63296,7 +63296,7 @@
       </c>
       <c r="S727" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -63381,7 +63381,7 @@
       </c>
       <c r="S728" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -63466,7 +63466,7 @@
       </c>
       <c r="S729" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -63551,7 +63551,7 @@
       </c>
       <c r="S730" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -63636,7 +63636,7 @@
       </c>
       <c r="S731" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -63721,7 +63721,7 @@
       </c>
       <c r="S732" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -63806,7 +63806,7 @@
       </c>
       <c r="S733" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -63891,7 +63891,7 @@
       </c>
       <c r="S734" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -63976,7 +63976,7 @@
       </c>
       <c r="S735" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -64061,7 +64061,7 @@
       </c>
       <c r="S736" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -64146,7 +64146,7 @@
       </c>
       <c r="S737" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -64231,7 +64231,7 @@
       </c>
       <c r="S738" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -64316,7 +64316,7 @@
       </c>
       <c r="S739" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -64401,7 +64401,7 @@
       </c>
       <c r="S740" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -64486,7 +64486,7 @@
       </c>
       <c r="S741" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -64571,7 +64571,7 @@
       </c>
       <c r="S742" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -64660,7 +64660,7 @@
       </c>
       <c r="S743" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -64749,7 +64749,7 @@
       </c>
       <c r="S744" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -64838,7 +64838,7 @@
       </c>
       <c r="S745" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -64927,7 +64927,7 @@
       </c>
       <c r="S746" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -65016,7 +65016,7 @@
       </c>
       <c r="S747" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -65105,7 +65105,7 @@
       </c>
       <c r="S748" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -65194,7 +65194,7 @@
       </c>
       <c r="S749" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -65283,7 +65283,7 @@
       </c>
       <c r="S750" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -65372,7 +65372,7 @@
       </c>
       <c r="S751" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -65461,7 +65461,7 @@
       </c>
       <c r="S752" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -65550,7 +65550,7 @@
       </c>
       <c r="S753" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -65639,7 +65639,7 @@
       </c>
       <c r="S754" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -65728,7 +65728,7 @@
       </c>
       <c r="S755" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -65817,7 +65817,7 @@
       </c>
       <c r="S756" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -65906,7 +65906,7 @@
       </c>
       <c r="S757" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -65995,7 +65995,7 @@
       </c>
       <c r="S758" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -66084,7 +66084,7 @@
       </c>
       <c r="S759" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -66173,7 +66173,7 @@
       </c>
       <c r="S760" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -66262,7 +66262,7 @@
       </c>
       <c r="S761" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -66351,7 +66351,7 @@
       </c>
       <c r="S762" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -66436,7 +66436,7 @@
       </c>
       <c r="S763" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -66521,7 +66521,7 @@
       </c>
       <c r="S764" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -66606,7 +66606,7 @@
       </c>
       <c r="S765" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -66691,7 +66691,7 @@
       </c>
       <c r="S766" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -66776,7 +66776,7 @@
       </c>
       <c r="S767" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -66861,7 +66861,7 @@
       </c>
       <c r="S768" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -66946,7 +66946,7 @@
       </c>
       <c r="S769" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -67031,7 +67031,7 @@
       </c>
       <c r="S770" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -67116,7 +67116,7 @@
       </c>
       <c r="S771" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -67201,7 +67201,7 @@
       </c>
       <c r="S772" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -67286,7 +67286,7 @@
       </c>
       <c r="S773" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -67375,7 +67375,7 @@
       </c>
       <c r="S774" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -67464,7 +67464,7 @@
       </c>
       <c r="S775" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -67553,7 +67553,7 @@
       </c>
       <c r="S776" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -67642,7 +67642,7 @@
       </c>
       <c r="S777" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -67731,7 +67731,7 @@
       </c>
       <c r="S778" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -67820,7 +67820,7 @@
       </c>
       <c r="S779" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -67909,7 +67909,7 @@
       </c>
       <c r="S780" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -67998,7 +67998,7 @@
       </c>
       <c r="S781" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -68087,7 +68087,7 @@
       </c>
       <c r="S782" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -68176,7 +68176,7 @@
       </c>
       <c r="S783" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -68261,7 +68261,7 @@
       </c>
       <c r="S784" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -68346,7 +68346,7 @@
       </c>
       <c r="S785" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -68431,7 +68431,7 @@
       </c>
       <c r="S786" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -68516,7 +68516,7 @@
       </c>
       <c r="S787" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -68601,7 +68601,7 @@
       </c>
       <c r="S788" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -68686,7 +68686,7 @@
       </c>
       <c r="S789" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -68771,7 +68771,7 @@
       </c>
       <c r="S790" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -68856,7 +68856,7 @@
       </c>
       <c r="S791" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -68941,7 +68941,7 @@
       </c>
       <c r="S792" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -69026,7 +69026,7 @@
       </c>
       <c r="S793" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -69111,7 +69111,7 @@
       </c>
       <c r="S794" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -69200,7 +69200,7 @@
       </c>
       <c r="S795" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -69289,7 +69289,7 @@
       </c>
       <c r="S796" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -69378,7 +69378,7 @@
       </c>
       <c r="S797" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -69467,7 +69467,7 @@
       </c>
       <c r="S798" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -69556,7 +69556,7 @@
       </c>
       <c r="S799" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -69645,7 +69645,7 @@
       </c>
       <c r="S800" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -69734,7 +69734,7 @@
       </c>
       <c r="S801" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -69823,7 +69823,7 @@
       </c>
       <c r="S802" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -69912,7 +69912,7 @@
       </c>
       <c r="S803" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -70001,7 +70001,7 @@
       </c>
       <c r="S804" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -70086,7 +70086,7 @@
       </c>
       <c r="S805" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -70171,7 +70171,7 @@
       </c>
       <c r="S806" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -70256,7 +70256,7 @@
       </c>
       <c r="S807" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -70341,7 +70341,7 @@
       </c>
       <c r="S808" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -70426,7 +70426,7 @@
       </c>
       <c r="S809" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -70511,7 +70511,7 @@
       </c>
       <c r="S810" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -70596,7 +70596,7 @@
       </c>
       <c r="S811" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -70681,7 +70681,7 @@
       </c>
       <c r="S812" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -70766,7 +70766,7 @@
       </c>
       <c r="S813" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -70851,7 +70851,7 @@
       </c>
       <c r="S814" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -70936,7 +70936,7 @@
       </c>
       <c r="S815" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -71021,7 +71021,7 @@
       </c>
       <c r="S816" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -71106,7 +71106,7 @@
       </c>
       <c r="S817" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -71191,7 +71191,7 @@
       </c>
       <c r="S818" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -71276,7 +71276,7 @@
       </c>
       <c r="S819" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -71361,7 +71361,7 @@
       </c>
       <c r="S820" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -71446,7 +71446,7 @@
       </c>
       <c r="S821" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -71531,7 +71531,7 @@
       </c>
       <c r="S822" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -71616,7 +71616,7 @@
       </c>
       <c r="S823" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -71701,7 +71701,7 @@
       </c>
       <c r="S824" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -71786,7 +71786,7 @@
       </c>
       <c r="S825" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -71871,7 +71871,7 @@
       </c>
       <c r="S826" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -71960,7 +71960,7 @@
       </c>
       <c r="S827" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -72049,7 +72049,7 @@
       </c>
       <c r="S828" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -72138,7 +72138,7 @@
       </c>
       <c r="S829" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -72227,7 +72227,7 @@
       </c>
       <c r="S830" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -72316,7 +72316,7 @@
       </c>
       <c r="S831" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -72405,7 +72405,7 @@
       </c>
       <c r="S832" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -72494,7 +72494,7 @@
       </c>
       <c r="S833" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -72583,7 +72583,7 @@
       </c>
       <c r="S834" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -72672,7 +72672,7 @@
       </c>
       <c r="S835" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -72761,7 +72761,7 @@
       </c>
       <c r="S836" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -72850,7 +72850,7 @@
       </c>
       <c r="S837" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -72939,7 +72939,7 @@
       </c>
       <c r="S838" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -73028,7 +73028,7 @@
       </c>
       <c r="S839" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -73117,7 +73117,7 @@
       </c>
       <c r="S840" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -73206,7 +73206,7 @@
       </c>
       <c r="S841" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -73295,7 +73295,7 @@
       </c>
       <c r="S842" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -73384,7 +73384,7 @@
       </c>
       <c r="S843" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -73473,7 +73473,7 @@
       </c>
       <c r="S844" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -73562,7 +73562,7 @@
       </c>
       <c r="S845" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -73651,7 +73651,7 @@
       </c>
       <c r="S846" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -73736,7 +73736,7 @@
       </c>
       <c r="S847" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -73821,7 +73821,7 @@
       </c>
       <c r="S848" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -73906,7 +73906,7 @@
       </c>
       <c r="S849" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -73991,7 +73991,7 @@
       </c>
       <c r="S850" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -74076,7 +74076,7 @@
       </c>
       <c r="S851" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -74161,7 +74161,7 @@
       </c>
       <c r="S852" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -74246,7 +74246,7 @@
       </c>
       <c r="S853" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -74331,7 +74331,7 @@
       </c>
       <c r="S854" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -74416,7 +74416,7 @@
       </c>
       <c r="S855" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -74501,7 +74501,7 @@
       </c>
       <c r="S856" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -74586,7 +74586,7 @@
       </c>
       <c r="S857" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -74671,7 +74671,7 @@
       </c>
       <c r="S858" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -74756,7 +74756,7 @@
       </c>
       <c r="S859" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -74841,7 +74841,7 @@
       </c>
       <c r="S860" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -74926,7 +74926,7 @@
       </c>
       <c r="S861" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -75011,7 +75011,7 @@
       </c>
       <c r="S862" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -75096,7 +75096,7 @@
       </c>
       <c r="S863" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -75181,7 +75181,7 @@
       </c>
       <c r="S864" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -75266,7 +75266,7 @@
       </c>
       <c r="S865" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -75351,7 +75351,7 @@
       </c>
       <c r="S866" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -75436,7 +75436,7 @@
       </c>
       <c r="S867" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -75521,7 +75521,7 @@
       </c>
       <c r="S868" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -75610,7 +75610,7 @@
       </c>
       <c r="S869" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -75699,7 +75699,7 @@
       </c>
       <c r="S870" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -75788,7 +75788,7 @@
       </c>
       <c r="S871" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -75877,7 +75877,7 @@
       </c>
       <c r="S872" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -75966,7 +75966,7 @@
       </c>
       <c r="S873" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -76055,7 +76055,7 @@
       </c>
       <c r="S874" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -76144,7 +76144,7 @@
       </c>
       <c r="S875" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -76233,7 +76233,7 @@
       </c>
       <c r="S876" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -76322,7 +76322,7 @@
       </c>
       <c r="S877" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -76411,7 +76411,7 @@
       </c>
       <c r="S878" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -76500,7 +76500,7 @@
       </c>
       <c r="S879" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -76589,7 +76589,7 @@
       </c>
       <c r="S880" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -76678,7 +76678,7 @@
       </c>
       <c r="S881" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -76767,7 +76767,7 @@
       </c>
       <c r="S882" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -76856,7 +76856,7 @@
       </c>
       <c r="S883" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -76945,7 +76945,7 @@
       </c>
       <c r="S884" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -77034,7 +77034,7 @@
       </c>
       <c r="S885" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -77123,7 +77123,7 @@
       </c>
       <c r="S886" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -77212,7 +77212,7 @@
       </c>
       <c r="S887" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -77301,7 +77301,7 @@
       </c>
       <c r="S888" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -77433,7 +77433,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:02Z</t>
+          <t>2026-08-10T21:11:07Z</t>
         </is>
       </c>
     </row>
@@ -77513,7 +77513,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-08-09T21:02:02Z"}</t>
+          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-08-10T21:11:07Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12625,7 +12625,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -13936,7 +13936,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14446,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -15041,7 +15041,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15296,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16008,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -17161,7 +17161,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -17416,7 +17416,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -17501,7 +17501,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17586,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17671,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -17841,7 +17841,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -18100,7 +18100,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -18367,7 +18367,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -18812,7 +18812,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -19326,7 +19326,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -20176,7 +20176,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -20261,7 +20261,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -20686,7 +20686,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -20941,7 +20941,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -21026,7 +21026,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -21281,7 +21281,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -21536,7 +21536,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -21706,7 +21706,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -21795,7 +21795,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -22062,7 +22062,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -22151,7 +22151,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -22240,7 +22240,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -22507,7 +22507,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22596,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -22685,7 +22685,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -22774,7 +22774,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -22952,7 +22952,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -23041,7 +23041,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -23130,7 +23130,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -23308,7 +23308,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -23397,7 +23397,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -23486,7 +23486,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -23575,7 +23575,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -23753,7 +23753,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24198,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -24287,7 +24287,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -24376,7 +24376,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -24461,7 +24461,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -24716,7 +24716,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -24886,7 +24886,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -24971,7 +24971,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25056,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -25226,7 +25226,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25396,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -25566,7 +25566,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -25736,7 +25736,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -25906,7 +25906,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -26076,7 +26076,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -26161,7 +26161,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -26335,7 +26335,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -26424,7 +26424,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -26602,7 +26602,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -26780,7 +26780,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -26869,7 +26869,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -26958,7 +26958,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -27225,7 +27225,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -27403,7 +27403,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -27492,7 +27492,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -27670,7 +27670,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -27759,7 +27759,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -27848,7 +27848,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -27937,7 +27937,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -28026,7 +28026,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -28196,7 +28196,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28281,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -28366,7 +28366,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -28451,7 +28451,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -28876,7 +28876,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -29046,7 +29046,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -29216,7 +29216,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -29301,7 +29301,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -29386,7 +29386,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -29471,7 +29471,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -29556,7 +29556,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -29641,7 +29641,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -29726,7 +29726,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -29811,7 +29811,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -29985,7 +29985,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -30341,7 +30341,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -30430,7 +30430,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -30608,7 +30608,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -31231,7 +31231,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -31498,7 +31498,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -31587,7 +31587,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -31676,7 +31676,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -31761,7 +31761,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -31846,7 +31846,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -31931,7 +31931,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -32101,7 +32101,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -32186,7 +32186,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -32271,7 +32271,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -32356,7 +32356,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -32441,7 +32441,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -32526,7 +32526,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -32611,7 +32611,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -32696,7 +32696,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -32951,7 +32951,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -33036,7 +33036,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -33291,7 +33291,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -33376,7 +33376,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -33461,7 +33461,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -33724,7 +33724,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -33813,7 +33813,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -33902,7 +33902,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -33991,7 +33991,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -34080,7 +34080,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -34169,7 +34169,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -34258,7 +34258,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -34347,7 +34347,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -34436,7 +34436,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -34525,7 +34525,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -34614,7 +34614,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -34703,7 +34703,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -34881,7 +34881,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -35148,7 +35148,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -35237,7 +35237,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -35326,7 +35326,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -35411,7 +35411,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -35496,7 +35496,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -35581,7 +35581,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -35836,7 +35836,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -36006,7 +36006,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -36091,7 +36091,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -36176,7 +36176,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -36261,7 +36261,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -36350,7 +36350,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -36439,7 +36439,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -36706,7 +36706,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -36795,7 +36795,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -36884,7 +36884,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -36973,7 +36973,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -37062,7 +37062,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -37151,7 +37151,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -37236,7 +37236,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -37321,7 +37321,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -37491,7 +37491,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -37576,7 +37576,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -37661,7 +37661,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -37746,7 +37746,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -37831,7 +37831,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -38001,7 +38001,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -38086,7 +38086,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -38256,7 +38256,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -38341,7 +38341,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -38426,7 +38426,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -38511,7 +38511,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -38596,7 +38596,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38681,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -38766,7 +38766,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -38851,7 +38851,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -38936,7 +38936,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -39021,7 +39021,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -39110,7 +39110,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -39199,7 +39199,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -39288,7 +39288,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -39377,7 +39377,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -39466,7 +39466,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -39644,7 +39644,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -39822,7 +39822,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -39911,7 +39911,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -40000,7 +40000,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -40089,7 +40089,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -40178,7 +40178,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -40267,7 +40267,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -40445,7 +40445,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -40534,7 +40534,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -40623,7 +40623,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -40712,7 +40712,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -40886,7 +40886,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -40971,7 +40971,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -41141,7 +41141,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -41226,7 +41226,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -41311,7 +41311,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -41396,7 +41396,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -41481,7 +41481,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -41566,7 +41566,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -41651,7 +41651,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -41736,7 +41736,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -41825,7 +41825,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -41914,7 +41914,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -42003,7 +42003,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -42092,7 +42092,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -42181,7 +42181,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -42270,7 +42270,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -42359,7 +42359,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -42448,7 +42448,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -42537,7 +42537,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -42626,7 +42626,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -42711,7 +42711,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -42796,7 +42796,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -42881,7 +42881,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -43051,7 +43051,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -43221,7 +43221,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -43306,7 +43306,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -43391,7 +43391,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -43476,7 +43476,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -43561,7 +43561,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -43646,7 +43646,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -43731,7 +43731,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -43816,7 +43816,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -43901,7 +43901,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -43986,7 +43986,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -44071,7 +44071,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -44156,7 +44156,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -44241,7 +44241,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -44411,7 +44411,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -44496,7 +44496,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -44585,7 +44585,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -44674,7 +44674,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -44763,7 +44763,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -44852,7 +44852,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -44941,7 +44941,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -45030,7 +45030,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -45119,7 +45119,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -45208,7 +45208,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -45297,7 +45297,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -45386,7 +45386,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -45475,7 +45475,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -45564,7 +45564,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -45653,7 +45653,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -45742,7 +45742,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -45831,7 +45831,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -45920,7 +45920,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -46009,7 +46009,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -46098,7 +46098,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -46187,7 +46187,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -46276,7 +46276,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -46361,7 +46361,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -46446,7 +46446,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -46531,7 +46531,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -46616,7 +46616,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -46701,7 +46701,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -46786,7 +46786,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -46871,7 +46871,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -46956,7 +46956,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -47041,7 +47041,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -47126,7 +47126,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -47211,7 +47211,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -47300,7 +47300,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -47389,7 +47389,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -47478,7 +47478,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -47567,7 +47567,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -47656,7 +47656,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -47745,7 +47745,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -47834,7 +47834,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -47923,7 +47923,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -48012,7 +48012,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -48101,7 +48101,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -48186,7 +48186,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -48271,7 +48271,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -48356,7 +48356,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -48441,7 +48441,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -48526,7 +48526,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -48696,7 +48696,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -48781,7 +48781,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -48866,7 +48866,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -48951,7 +48951,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -49036,7 +49036,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -49125,7 +49125,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -49214,7 +49214,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -49303,7 +49303,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -49392,7 +49392,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -49481,7 +49481,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -49570,7 +49570,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -49659,7 +49659,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -49748,7 +49748,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -49837,7 +49837,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -49926,7 +49926,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -50011,7 +50011,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -50096,7 +50096,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -50181,7 +50181,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -50266,7 +50266,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -50436,7 +50436,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -50521,7 +50521,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -50606,7 +50606,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -50691,7 +50691,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -50776,7 +50776,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -50861,7 +50861,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -50946,7 +50946,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -51031,7 +51031,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -51116,7 +51116,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -51201,7 +51201,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -51286,7 +51286,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -51371,7 +51371,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -51456,7 +51456,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -51541,7 +51541,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -51626,7 +51626,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -51711,7 +51711,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -51796,7 +51796,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -51885,7 +51885,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -51974,7 +51974,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -52063,7 +52063,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -52152,7 +52152,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -52241,7 +52241,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -52330,7 +52330,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -52419,7 +52419,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -52508,7 +52508,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -52597,7 +52597,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -52686,7 +52686,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -52775,7 +52775,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -52864,7 +52864,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -52953,7 +52953,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -53042,7 +53042,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -53131,7 +53131,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -53220,7 +53220,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -53309,7 +53309,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -53398,7 +53398,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -53487,7 +53487,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -53576,7 +53576,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -53661,7 +53661,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -53746,7 +53746,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -53831,7 +53831,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -53916,7 +53916,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -54001,7 +54001,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -54086,7 +54086,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -54171,7 +54171,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -54256,7 +54256,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -54426,7 +54426,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -54511,7 +54511,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -54596,7 +54596,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -54681,7 +54681,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -54766,7 +54766,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -54851,7 +54851,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -54936,7 +54936,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -55021,7 +55021,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -55106,7 +55106,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -55191,7 +55191,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -55276,7 +55276,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -55361,7 +55361,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -55446,7 +55446,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -55531,7 +55531,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -55616,7 +55616,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -55701,7 +55701,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -55786,7 +55786,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -55871,7 +55871,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -55956,7 +55956,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -56041,7 +56041,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -56126,7 +56126,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -56211,7 +56211,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -56296,7 +56296,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -56381,7 +56381,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -56466,7 +56466,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -56551,7 +56551,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -56636,7 +56636,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -56721,7 +56721,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56806,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -56891,7 +56891,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -56976,7 +56976,7 @@
       </c>
       <c r="S655" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -57061,7 +57061,7 @@
       </c>
       <c r="S656" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -57146,7 +57146,7 @@
       </c>
       <c r="S657" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -57231,7 +57231,7 @@
       </c>
       <c r="S658" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -57316,7 +57316,7 @@
       </c>
       <c r="S659" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -57401,7 +57401,7 @@
       </c>
       <c r="S660" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -57486,7 +57486,7 @@
       </c>
       <c r="S661" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -57571,7 +57571,7 @@
       </c>
       <c r="S662" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -57656,7 +57656,7 @@
       </c>
       <c r="S663" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -57741,7 +57741,7 @@
       </c>
       <c r="S664" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -57826,7 +57826,7 @@
       </c>
       <c r="S665" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -57911,7 +57911,7 @@
       </c>
       <c r="S666" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -57996,7 +57996,7 @@
       </c>
       <c r="S667" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -58081,7 +58081,7 @@
       </c>
       <c r="S668" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -58166,7 +58166,7 @@
       </c>
       <c r="S669" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -58251,7 +58251,7 @@
       </c>
       <c r="S670" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -58340,7 +58340,7 @@
       </c>
       <c r="S671" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -58429,7 +58429,7 @@
       </c>
       <c r="S672" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -58518,7 +58518,7 @@
       </c>
       <c r="S673" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -58607,7 +58607,7 @@
       </c>
       <c r="S674" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -58696,7 +58696,7 @@
       </c>
       <c r="S675" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -58785,7 +58785,7 @@
       </c>
       <c r="S676" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -58874,7 +58874,7 @@
       </c>
       <c r="S677" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -58963,7 +58963,7 @@
       </c>
       <c r="S678" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -59052,7 +59052,7 @@
       </c>
       <c r="S679" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -59141,7 +59141,7 @@
       </c>
       <c r="S680" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -59230,7 +59230,7 @@
       </c>
       <c r="S681" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -59319,7 +59319,7 @@
       </c>
       <c r="S682" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -59408,7 +59408,7 @@
       </c>
       <c r="S683" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -59497,7 +59497,7 @@
       </c>
       <c r="S684" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -59586,7 +59586,7 @@
       </c>
       <c r="S685" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -59675,7 +59675,7 @@
       </c>
       <c r="S686" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -59764,7 +59764,7 @@
       </c>
       <c r="S687" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -59853,7 +59853,7 @@
       </c>
       <c r="S688" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -59942,7 +59942,7 @@
       </c>
       <c r="S689" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -60031,7 +60031,7 @@
       </c>
       <c r="S690" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -60120,7 +60120,7 @@
       </c>
       <c r="S691" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -60209,7 +60209,7 @@
       </c>
       <c r="S692" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="S693" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -60387,7 +60387,7 @@
       </c>
       <c r="S694" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -60476,7 +60476,7 @@
       </c>
       <c r="S695" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -60565,7 +60565,7 @@
       </c>
       <c r="S696" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -60654,7 +60654,7 @@
       </c>
       <c r="S697" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -60743,7 +60743,7 @@
       </c>
       <c r="S698" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -60832,7 +60832,7 @@
       </c>
       <c r="S699" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -60921,7 +60921,7 @@
       </c>
       <c r="S700" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -61010,7 +61010,7 @@
       </c>
       <c r="S701" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -61099,7 +61099,7 @@
       </c>
       <c r="S702" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -61188,7 +61188,7 @@
       </c>
       <c r="S703" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -61277,7 +61277,7 @@
       </c>
       <c r="S704" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -61366,7 +61366,7 @@
       </c>
       <c r="S705" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -61455,7 +61455,7 @@
       </c>
       <c r="S706" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -61544,7 +61544,7 @@
       </c>
       <c r="S707" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -61633,7 +61633,7 @@
       </c>
       <c r="S708" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -61722,7 +61722,7 @@
       </c>
       <c r="S709" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -61811,7 +61811,7 @@
       </c>
       <c r="S710" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -61900,7 +61900,7 @@
       </c>
       <c r="S711" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -61989,7 +61989,7 @@
       </c>
       <c r="S712" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -62078,7 +62078,7 @@
       </c>
       <c r="S713" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -62167,7 +62167,7 @@
       </c>
       <c r="S714" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -62256,7 +62256,7 @@
       </c>
       <c r="S715" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -62345,7 +62345,7 @@
       </c>
       <c r="S716" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -62434,7 +62434,7 @@
       </c>
       <c r="S717" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -62523,7 +62523,7 @@
       </c>
       <c r="S718" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -62612,7 +62612,7 @@
       </c>
       <c r="S719" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -62701,7 +62701,7 @@
       </c>
       <c r="S720" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -62786,7 +62786,7 @@
       </c>
       <c r="S721" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -62871,7 +62871,7 @@
       </c>
       <c r="S722" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -62956,7 +62956,7 @@
       </c>
       <c r="S723" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -63041,7 +63041,7 @@
       </c>
       <c r="S724" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -63126,7 +63126,7 @@
       </c>
       <c r="S725" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -63211,7 +63211,7 @@
       </c>
       <c r="S726" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -63296,7 +63296,7 @@
       </c>
       <c r="S727" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -63381,7 +63381,7 @@
       </c>
       <c r="S728" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -63466,7 +63466,7 @@
       </c>
       <c r="S729" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -63551,7 +63551,7 @@
       </c>
       <c r="S730" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -63636,7 +63636,7 @@
       </c>
       <c r="S731" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -63721,7 +63721,7 @@
       </c>
       <c r="S732" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -63806,7 +63806,7 @@
       </c>
       <c r="S733" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -63891,7 +63891,7 @@
       </c>
       <c r="S734" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -63976,7 +63976,7 @@
       </c>
       <c r="S735" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -64061,7 +64061,7 @@
       </c>
       <c r="S736" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -64146,7 +64146,7 @@
       </c>
       <c r="S737" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -64231,7 +64231,7 @@
       </c>
       <c r="S738" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -64316,7 +64316,7 @@
       </c>
       <c r="S739" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -64401,7 +64401,7 @@
       </c>
       <c r="S740" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -64486,7 +64486,7 @@
       </c>
       <c r="S741" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -64571,7 +64571,7 @@
       </c>
       <c r="S742" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -64660,7 +64660,7 @@
       </c>
       <c r="S743" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -64749,7 +64749,7 @@
       </c>
       <c r="S744" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -64838,7 +64838,7 @@
       </c>
       <c r="S745" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -64927,7 +64927,7 @@
       </c>
       <c r="S746" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -65016,7 +65016,7 @@
       </c>
       <c r="S747" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -65105,7 +65105,7 @@
       </c>
       <c r="S748" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -65194,7 +65194,7 @@
       </c>
       <c r="S749" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -65283,7 +65283,7 @@
       </c>
       <c r="S750" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -65372,7 +65372,7 @@
       </c>
       <c r="S751" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -65461,7 +65461,7 @@
       </c>
       <c r="S752" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -65550,7 +65550,7 @@
       </c>
       <c r="S753" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -65639,7 +65639,7 @@
       </c>
       <c r="S754" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -65728,7 +65728,7 @@
       </c>
       <c r="S755" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -65817,7 +65817,7 @@
       </c>
       <c r="S756" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -65906,7 +65906,7 @@
       </c>
       <c r="S757" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -65995,7 +65995,7 @@
       </c>
       <c r="S758" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -66084,7 +66084,7 @@
       </c>
       <c r="S759" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -66173,7 +66173,7 @@
       </c>
       <c r="S760" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -66262,7 +66262,7 @@
       </c>
       <c r="S761" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -66351,7 +66351,7 @@
       </c>
       <c r="S762" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -66436,7 +66436,7 @@
       </c>
       <c r="S763" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -66521,7 +66521,7 @@
       </c>
       <c r="S764" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -66606,7 +66606,7 @@
       </c>
       <c r="S765" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -66691,7 +66691,7 @@
       </c>
       <c r="S766" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -66776,7 +66776,7 @@
       </c>
       <c r="S767" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -66861,7 +66861,7 @@
       </c>
       <c r="S768" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -66946,7 +66946,7 @@
       </c>
       <c r="S769" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -67031,7 +67031,7 @@
       </c>
       <c r="S770" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -67116,7 +67116,7 @@
       </c>
       <c r="S771" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -67201,7 +67201,7 @@
       </c>
       <c r="S772" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -67286,7 +67286,7 @@
       </c>
       <c r="S773" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -67375,7 +67375,7 @@
       </c>
       <c r="S774" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -67464,7 +67464,7 @@
       </c>
       <c r="S775" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -67553,7 +67553,7 @@
       </c>
       <c r="S776" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -67642,7 +67642,7 @@
       </c>
       <c r="S777" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -67731,7 +67731,7 @@
       </c>
       <c r="S778" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -67820,7 +67820,7 @@
       </c>
       <c r="S779" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -67909,7 +67909,7 @@
       </c>
       <c r="S780" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -67998,7 +67998,7 @@
       </c>
       <c r="S781" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -68087,7 +68087,7 @@
       </c>
       <c r="S782" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -68176,7 +68176,7 @@
       </c>
       <c r="S783" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -68261,7 +68261,7 @@
       </c>
       <c r="S784" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -68346,7 +68346,7 @@
       </c>
       <c r="S785" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -68431,7 +68431,7 @@
       </c>
       <c r="S786" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -68516,7 +68516,7 @@
       </c>
       <c r="S787" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -68601,7 +68601,7 @@
       </c>
       <c r="S788" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -68686,7 +68686,7 @@
       </c>
       <c r="S789" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -68771,7 +68771,7 @@
       </c>
       <c r="S790" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -68856,7 +68856,7 @@
       </c>
       <c r="S791" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -68941,7 +68941,7 @@
       </c>
       <c r="S792" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -69026,7 +69026,7 @@
       </c>
       <c r="S793" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -69111,7 +69111,7 @@
       </c>
       <c r="S794" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -69200,7 +69200,7 @@
       </c>
       <c r="S795" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -69289,7 +69289,7 @@
       </c>
       <c r="S796" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -69378,7 +69378,7 @@
       </c>
       <c r="S797" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -69467,7 +69467,7 @@
       </c>
       <c r="S798" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -69556,7 +69556,7 @@
       </c>
       <c r="S799" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -69645,7 +69645,7 @@
       </c>
       <c r="S800" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -69734,7 +69734,7 @@
       </c>
       <c r="S801" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -69823,7 +69823,7 @@
       </c>
       <c r="S802" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -69912,7 +69912,7 @@
       </c>
       <c r="S803" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -70001,7 +70001,7 @@
       </c>
       <c r="S804" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -70086,7 +70086,7 @@
       </c>
       <c r="S805" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -70171,7 +70171,7 @@
       </c>
       <c r="S806" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -70256,7 +70256,7 @@
       </c>
       <c r="S807" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -70341,7 +70341,7 @@
       </c>
       <c r="S808" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -70426,7 +70426,7 @@
       </c>
       <c r="S809" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -70511,7 +70511,7 @@
       </c>
       <c r="S810" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -70596,7 +70596,7 @@
       </c>
       <c r="S811" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -70681,7 +70681,7 @@
       </c>
       <c r="S812" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -70766,7 +70766,7 @@
       </c>
       <c r="S813" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -70851,7 +70851,7 @@
       </c>
       <c r="S814" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -70936,7 +70936,7 @@
       </c>
       <c r="S815" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -71021,7 +71021,7 @@
       </c>
       <c r="S816" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -71106,7 +71106,7 @@
       </c>
       <c r="S817" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -71191,7 +71191,7 @@
       </c>
       <c r="S818" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -71276,7 +71276,7 @@
       </c>
       <c r="S819" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -71361,7 +71361,7 @@
       </c>
       <c r="S820" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -71446,7 +71446,7 @@
       </c>
       <c r="S821" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -71531,7 +71531,7 @@
       </c>
       <c r="S822" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -71616,7 +71616,7 @@
       </c>
       <c r="S823" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -71701,7 +71701,7 @@
       </c>
       <c r="S824" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -71786,7 +71786,7 @@
       </c>
       <c r="S825" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -71871,7 +71871,7 @@
       </c>
       <c r="S826" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -71960,7 +71960,7 @@
       </c>
       <c r="S827" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -72049,7 +72049,7 @@
       </c>
       <c r="S828" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -72138,7 +72138,7 @@
       </c>
       <c r="S829" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -72227,7 +72227,7 @@
       </c>
       <c r="S830" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -72316,7 +72316,7 @@
       </c>
       <c r="S831" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -72405,7 +72405,7 @@
       </c>
       <c r="S832" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -72494,7 +72494,7 @@
       </c>
       <c r="S833" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -72583,7 +72583,7 @@
       </c>
       <c r="S834" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -72672,7 +72672,7 @@
       </c>
       <c r="S835" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -72761,7 +72761,7 @@
       </c>
       <c r="S836" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -72850,7 +72850,7 @@
       </c>
       <c r="S837" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -72939,7 +72939,7 @@
       </c>
       <c r="S838" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -73028,7 +73028,7 @@
       </c>
       <c r="S839" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -73117,7 +73117,7 @@
       </c>
       <c r="S840" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -73206,7 +73206,7 @@
       </c>
       <c r="S841" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -73295,7 +73295,7 @@
       </c>
       <c r="S842" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -73384,7 +73384,7 @@
       </c>
       <c r="S843" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -73473,7 +73473,7 @@
       </c>
       <c r="S844" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -73562,7 +73562,7 @@
       </c>
       <c r="S845" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -73651,7 +73651,7 @@
       </c>
       <c r="S846" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -73736,7 +73736,7 @@
       </c>
       <c r="S847" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -73821,7 +73821,7 @@
       </c>
       <c r="S848" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -73906,7 +73906,7 @@
       </c>
       <c r="S849" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -73991,7 +73991,7 @@
       </c>
       <c r="S850" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -74076,7 +74076,7 @@
       </c>
       <c r="S851" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -74161,7 +74161,7 @@
       </c>
       <c r="S852" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -74246,7 +74246,7 @@
       </c>
       <c r="S853" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -74331,7 +74331,7 @@
       </c>
       <c r="S854" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -74416,7 +74416,7 @@
       </c>
       <c r="S855" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -74501,7 +74501,7 @@
       </c>
       <c r="S856" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -74586,7 +74586,7 @@
       </c>
       <c r="S857" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -74671,7 +74671,7 @@
       </c>
       <c r="S858" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -74756,7 +74756,7 @@
       </c>
       <c r="S859" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -74841,7 +74841,7 @@
       </c>
       <c r="S860" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -74926,7 +74926,7 @@
       </c>
       <c r="S861" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -75011,7 +75011,7 @@
       </c>
       <c r="S862" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -75096,7 +75096,7 @@
       </c>
       <c r="S863" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -75181,7 +75181,7 @@
       </c>
       <c r="S864" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -75266,7 +75266,7 @@
       </c>
       <c r="S865" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -75351,7 +75351,7 @@
       </c>
       <c r="S866" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -75436,7 +75436,7 @@
       </c>
       <c r="S867" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -75521,7 +75521,7 @@
       </c>
       <c r="S868" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -75610,7 +75610,7 @@
       </c>
       <c r="S869" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -75699,7 +75699,7 @@
       </c>
       <c r="S870" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -75788,7 +75788,7 @@
       </c>
       <c r="S871" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -75877,7 +75877,7 @@
       </c>
       <c r="S872" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -75966,7 +75966,7 @@
       </c>
       <c r="S873" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -76055,7 +76055,7 @@
       </c>
       <c r="S874" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -76144,7 +76144,7 @@
       </c>
       <c r="S875" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -76233,7 +76233,7 @@
       </c>
       <c r="S876" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -76322,7 +76322,7 @@
       </c>
       <c r="S877" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -76411,7 +76411,7 @@
       </c>
       <c r="S878" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -76500,7 +76500,7 @@
       </c>
       <c r="S879" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -76589,7 +76589,7 @@
       </c>
       <c r="S880" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -76678,7 +76678,7 @@
       </c>
       <c r="S881" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -76767,7 +76767,7 @@
       </c>
       <c r="S882" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -76856,7 +76856,7 @@
       </c>
       <c r="S883" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -76945,7 +76945,7 @@
       </c>
       <c r="S884" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -77034,7 +77034,7 @@
       </c>
       <c r="S885" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -77123,7 +77123,7 @@
       </c>
       <c r="S886" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -77212,7 +77212,7 @@
       </c>
       <c r="S887" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -77301,7 +77301,7 @@
       </c>
       <c r="S888" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -77433,7 +77433,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:34Z</t>
+          <t>2026-08-14T20:55:16Z</t>
         </is>
       </c>
     </row>
@@ -77513,7 +77513,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-08-13T21:12:34Z"}</t>
+          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-08-14T20:55:16Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12625,7 +12625,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -13936,7 +13936,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14446,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -15041,7 +15041,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15296,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16008,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -17161,7 +17161,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -17416,7 +17416,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -17501,7 +17501,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17586,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17671,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -17841,7 +17841,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -18100,7 +18100,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -18367,7 +18367,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -18812,7 +18812,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -19326,7 +19326,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -20176,7 +20176,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -20261,7 +20261,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -20686,7 +20686,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -20941,7 +20941,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -21026,7 +21026,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -21281,7 +21281,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -21536,7 +21536,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -21706,7 +21706,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -21795,7 +21795,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -22062,7 +22062,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -22151,7 +22151,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -22240,7 +22240,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -22507,7 +22507,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22596,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -22685,7 +22685,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -22774,7 +22774,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -22952,7 +22952,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -23041,7 +23041,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -23130,7 +23130,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -23308,7 +23308,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -23397,7 +23397,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -23486,7 +23486,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -23575,7 +23575,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -23753,7 +23753,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24198,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -24287,7 +24287,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -24376,7 +24376,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -24461,7 +24461,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -24716,7 +24716,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -24886,7 +24886,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -24971,7 +24971,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25056,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -25226,7 +25226,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25396,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -25566,7 +25566,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -25736,7 +25736,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -25906,7 +25906,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -26076,7 +26076,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -26161,7 +26161,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -26335,7 +26335,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -26424,7 +26424,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -26602,7 +26602,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -26780,7 +26780,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -26869,7 +26869,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -26958,7 +26958,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -27225,7 +27225,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -27403,7 +27403,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -27492,7 +27492,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -27670,7 +27670,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -27759,7 +27759,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -27848,7 +27848,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -27937,7 +27937,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -28026,7 +28026,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -28196,7 +28196,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28281,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -28366,7 +28366,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -28451,7 +28451,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -28876,7 +28876,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -29046,7 +29046,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -29216,7 +29216,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -29301,7 +29301,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -29386,7 +29386,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -29471,7 +29471,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -29556,7 +29556,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -29641,7 +29641,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -29726,7 +29726,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -29811,7 +29811,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -29985,7 +29985,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -30341,7 +30341,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -30430,7 +30430,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -30608,7 +30608,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -31231,7 +31231,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -31498,7 +31498,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -31587,7 +31587,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -31676,7 +31676,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -31761,7 +31761,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -31846,7 +31846,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -31931,7 +31931,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -32101,7 +32101,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -32186,7 +32186,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -32271,7 +32271,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -32356,7 +32356,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -32441,7 +32441,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -32526,7 +32526,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -32611,7 +32611,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -32696,7 +32696,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -32951,7 +32951,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -33036,7 +33036,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -33291,7 +33291,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -33376,7 +33376,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -33461,7 +33461,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -33724,7 +33724,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -33813,7 +33813,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -33902,7 +33902,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -33991,7 +33991,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -34080,7 +34080,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -34169,7 +34169,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -34258,7 +34258,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -34347,7 +34347,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -34436,7 +34436,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -34525,7 +34525,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -34614,7 +34614,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -34703,7 +34703,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -34881,7 +34881,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -35148,7 +35148,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -35237,7 +35237,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -35326,7 +35326,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -35411,7 +35411,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -35496,7 +35496,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -35581,7 +35581,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -35836,7 +35836,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -36006,7 +36006,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -36091,7 +36091,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -36176,7 +36176,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -36261,7 +36261,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -36350,7 +36350,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -36439,7 +36439,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -36706,7 +36706,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -36795,7 +36795,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -36884,7 +36884,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -36973,7 +36973,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -37062,7 +37062,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -37151,7 +37151,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -37236,7 +37236,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -37321,7 +37321,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -37491,7 +37491,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -37576,7 +37576,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -37661,7 +37661,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -37746,7 +37746,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -37831,7 +37831,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -38001,7 +38001,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -38086,7 +38086,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -38256,7 +38256,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -38341,7 +38341,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -38426,7 +38426,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -38511,7 +38511,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -38596,7 +38596,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38681,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -38766,7 +38766,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -38851,7 +38851,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -38936,7 +38936,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -39021,7 +39021,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -39110,7 +39110,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -39199,7 +39199,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -39288,7 +39288,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -39377,7 +39377,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -39466,7 +39466,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -39644,7 +39644,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -39822,7 +39822,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -39911,7 +39911,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -40000,7 +40000,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -40089,7 +40089,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -40178,7 +40178,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -40267,7 +40267,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -40445,7 +40445,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -40534,7 +40534,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -40623,7 +40623,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -40712,7 +40712,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -40886,7 +40886,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -40971,7 +40971,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -41141,7 +41141,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -41226,7 +41226,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -41311,7 +41311,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -41396,7 +41396,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -41481,7 +41481,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -41566,7 +41566,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -41651,7 +41651,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -41736,7 +41736,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -41825,7 +41825,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -41914,7 +41914,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -42003,7 +42003,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -42092,7 +42092,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -42181,7 +42181,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -42270,7 +42270,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -42359,7 +42359,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -42448,7 +42448,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -42537,7 +42537,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -42626,7 +42626,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -42711,7 +42711,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -42796,7 +42796,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -42881,7 +42881,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -43051,7 +43051,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -43221,7 +43221,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -43306,7 +43306,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -43391,7 +43391,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -43476,7 +43476,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -43561,7 +43561,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -43646,7 +43646,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -43731,7 +43731,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -43816,7 +43816,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -43901,7 +43901,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -43986,7 +43986,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -44071,7 +44071,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -44156,7 +44156,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -44241,7 +44241,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -44411,7 +44411,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -44496,7 +44496,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -44585,7 +44585,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -44674,7 +44674,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -44763,7 +44763,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -44852,7 +44852,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -44941,7 +44941,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -45030,7 +45030,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -45119,7 +45119,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -45208,7 +45208,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -45297,7 +45297,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -45386,7 +45386,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -45475,7 +45475,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -45564,7 +45564,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -45653,7 +45653,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -45742,7 +45742,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -45831,7 +45831,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -45920,7 +45920,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -46009,7 +46009,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -46098,7 +46098,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -46187,7 +46187,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -46276,7 +46276,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -46361,7 +46361,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -46446,7 +46446,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -46531,7 +46531,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -46616,7 +46616,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -46701,7 +46701,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -46786,7 +46786,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -46871,7 +46871,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -46956,7 +46956,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -47041,7 +47041,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -47126,7 +47126,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -47211,7 +47211,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -47300,7 +47300,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -47389,7 +47389,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -47478,7 +47478,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -47567,7 +47567,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -47656,7 +47656,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -47745,7 +47745,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -47834,7 +47834,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -47923,7 +47923,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -48012,7 +48012,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -48101,7 +48101,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -48186,7 +48186,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -48271,7 +48271,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -48356,7 +48356,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -48441,7 +48441,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -48526,7 +48526,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -48696,7 +48696,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -48781,7 +48781,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -48866,7 +48866,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -48951,7 +48951,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -49036,7 +49036,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -49125,7 +49125,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -49214,7 +49214,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -49303,7 +49303,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -49392,7 +49392,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -49481,7 +49481,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -49570,7 +49570,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -49659,7 +49659,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -49748,7 +49748,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -49837,7 +49837,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -49926,7 +49926,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -50011,7 +50011,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -50096,7 +50096,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -50181,7 +50181,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -50266,7 +50266,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -50436,7 +50436,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -50521,7 +50521,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -50606,7 +50606,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -50691,7 +50691,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -50776,7 +50776,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -50861,7 +50861,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -50946,7 +50946,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -51031,7 +51031,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -51116,7 +51116,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -51201,7 +51201,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -51286,7 +51286,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -51371,7 +51371,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -51456,7 +51456,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -51541,7 +51541,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -51626,7 +51626,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -51711,7 +51711,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -51796,7 +51796,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -51885,7 +51885,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -51974,7 +51974,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -52063,7 +52063,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -52152,7 +52152,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -52241,7 +52241,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -52330,7 +52330,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -52419,7 +52419,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -52508,7 +52508,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -52597,7 +52597,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -52686,7 +52686,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -52775,7 +52775,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -52864,7 +52864,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -52953,7 +52953,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -53042,7 +53042,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -53131,7 +53131,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -53220,7 +53220,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -53309,7 +53309,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -53398,7 +53398,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -53487,7 +53487,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -53576,7 +53576,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -53661,7 +53661,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -53746,7 +53746,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -53831,7 +53831,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -53916,7 +53916,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -54001,7 +54001,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -54086,7 +54086,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -54171,7 +54171,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -54256,7 +54256,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -54426,7 +54426,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -54511,7 +54511,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -54596,7 +54596,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -54681,7 +54681,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -54766,7 +54766,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -54851,7 +54851,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -54936,7 +54936,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -55021,7 +55021,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -55106,7 +55106,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -55191,7 +55191,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -55276,7 +55276,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -55361,7 +55361,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -55446,7 +55446,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -55531,7 +55531,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -55616,7 +55616,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -55701,7 +55701,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -55786,7 +55786,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -55871,7 +55871,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -55956,7 +55956,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -56041,7 +56041,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -56126,7 +56126,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -56211,7 +56211,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -56296,7 +56296,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -56381,7 +56381,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -56466,7 +56466,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -56551,7 +56551,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -56636,7 +56636,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -56721,7 +56721,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56806,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -56891,7 +56891,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -56976,7 +56976,7 @@
       </c>
       <c r="S655" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -57061,7 +57061,7 @@
       </c>
       <c r="S656" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -57146,7 +57146,7 @@
       </c>
       <c r="S657" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -57231,7 +57231,7 @@
       </c>
       <c r="S658" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -57316,7 +57316,7 @@
       </c>
       <c r="S659" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -57401,7 +57401,7 @@
       </c>
       <c r="S660" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -57486,7 +57486,7 @@
       </c>
       <c r="S661" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -57571,7 +57571,7 @@
       </c>
       <c r="S662" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -57656,7 +57656,7 @@
       </c>
       <c r="S663" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -57741,7 +57741,7 @@
       </c>
       <c r="S664" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -57826,7 +57826,7 @@
       </c>
       <c r="S665" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -57911,7 +57911,7 @@
       </c>
       <c r="S666" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -57996,7 +57996,7 @@
       </c>
       <c r="S667" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -58081,7 +58081,7 @@
       </c>
       <c r="S668" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -58166,7 +58166,7 @@
       </c>
       <c r="S669" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -58251,7 +58251,7 @@
       </c>
       <c r="S670" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -58340,7 +58340,7 @@
       </c>
       <c r="S671" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -58429,7 +58429,7 @@
       </c>
       <c r="S672" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -58518,7 +58518,7 @@
       </c>
       <c r="S673" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -58607,7 +58607,7 @@
       </c>
       <c r="S674" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -58696,7 +58696,7 @@
       </c>
       <c r="S675" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -58785,7 +58785,7 @@
       </c>
       <c r="S676" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -58874,7 +58874,7 @@
       </c>
       <c r="S677" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -58963,7 +58963,7 @@
       </c>
       <c r="S678" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -59052,7 +59052,7 @@
       </c>
       <c r="S679" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -59141,7 +59141,7 @@
       </c>
       <c r="S680" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -59230,7 +59230,7 @@
       </c>
       <c r="S681" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -59319,7 +59319,7 @@
       </c>
       <c r="S682" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -59408,7 +59408,7 @@
       </c>
       <c r="S683" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -59497,7 +59497,7 @@
       </c>
       <c r="S684" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -59586,7 +59586,7 @@
       </c>
       <c r="S685" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -59675,7 +59675,7 @@
       </c>
       <c r="S686" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -59764,7 +59764,7 @@
       </c>
       <c r="S687" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -59853,7 +59853,7 @@
       </c>
       <c r="S688" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -59942,7 +59942,7 @@
       </c>
       <c r="S689" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -60031,7 +60031,7 @@
       </c>
       <c r="S690" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -60120,7 +60120,7 @@
       </c>
       <c r="S691" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -60209,7 +60209,7 @@
       </c>
       <c r="S692" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="S693" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -60387,7 +60387,7 @@
       </c>
       <c r="S694" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -60476,7 +60476,7 @@
       </c>
       <c r="S695" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -60565,7 +60565,7 @@
       </c>
       <c r="S696" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -60654,7 +60654,7 @@
       </c>
       <c r="S697" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -60743,7 +60743,7 @@
       </c>
       <c r="S698" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -60832,7 +60832,7 @@
       </c>
       <c r="S699" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -60921,7 +60921,7 @@
       </c>
       <c r="S700" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -61010,7 +61010,7 @@
       </c>
       <c r="S701" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -61099,7 +61099,7 @@
       </c>
       <c r="S702" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -61188,7 +61188,7 @@
       </c>
       <c r="S703" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -61277,7 +61277,7 @@
       </c>
       <c r="S704" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -61366,7 +61366,7 @@
       </c>
       <c r="S705" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -61455,7 +61455,7 @@
       </c>
       <c r="S706" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -61544,7 +61544,7 @@
       </c>
       <c r="S707" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -61633,7 +61633,7 @@
       </c>
       <c r="S708" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -61722,7 +61722,7 @@
       </c>
       <c r="S709" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -61811,7 +61811,7 @@
       </c>
       <c r="S710" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -61900,7 +61900,7 @@
       </c>
       <c r="S711" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -61989,7 +61989,7 @@
       </c>
       <c r="S712" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -62078,7 +62078,7 @@
       </c>
       <c r="S713" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -62167,7 +62167,7 @@
       </c>
       <c r="S714" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -62256,7 +62256,7 @@
       </c>
       <c r="S715" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -62345,7 +62345,7 @@
       </c>
       <c r="S716" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -62434,7 +62434,7 @@
       </c>
       <c r="S717" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -62523,7 +62523,7 @@
       </c>
       <c r="S718" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -62612,7 +62612,7 @@
       </c>
       <c r="S719" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -62701,7 +62701,7 @@
       </c>
       <c r="S720" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -62786,7 +62786,7 @@
       </c>
       <c r="S721" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -62871,7 +62871,7 @@
       </c>
       <c r="S722" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -62956,7 +62956,7 @@
       </c>
       <c r="S723" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -63041,7 +63041,7 @@
       </c>
       <c r="S724" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -63126,7 +63126,7 @@
       </c>
       <c r="S725" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -63211,7 +63211,7 @@
       </c>
       <c r="S726" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -63296,7 +63296,7 @@
       </c>
       <c r="S727" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -63381,7 +63381,7 @@
       </c>
       <c r="S728" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -63466,7 +63466,7 @@
       </c>
       <c r="S729" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -63551,7 +63551,7 @@
       </c>
       <c r="S730" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -63636,7 +63636,7 @@
       </c>
       <c r="S731" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -63721,7 +63721,7 @@
       </c>
       <c r="S732" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -63806,7 +63806,7 @@
       </c>
       <c r="S733" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -63891,7 +63891,7 @@
       </c>
       <c r="S734" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -63976,7 +63976,7 @@
       </c>
       <c r="S735" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -64061,7 +64061,7 @@
       </c>
       <c r="S736" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -64146,7 +64146,7 @@
       </c>
       <c r="S737" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -64231,7 +64231,7 @@
       </c>
       <c r="S738" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -64316,7 +64316,7 @@
       </c>
       <c r="S739" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -64401,7 +64401,7 @@
       </c>
       <c r="S740" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -64486,7 +64486,7 @@
       </c>
       <c r="S741" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -64571,7 +64571,7 @@
       </c>
       <c r="S742" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -64660,7 +64660,7 @@
       </c>
       <c r="S743" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -64749,7 +64749,7 @@
       </c>
       <c r="S744" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -64838,7 +64838,7 @@
       </c>
       <c r="S745" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -64927,7 +64927,7 @@
       </c>
       <c r="S746" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -65016,7 +65016,7 @@
       </c>
       <c r="S747" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -65105,7 +65105,7 @@
       </c>
       <c r="S748" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -65194,7 +65194,7 @@
       </c>
       <c r="S749" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -65283,7 +65283,7 @@
       </c>
       <c r="S750" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -65372,7 +65372,7 @@
       </c>
       <c r="S751" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -65461,7 +65461,7 @@
       </c>
       <c r="S752" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -65550,7 +65550,7 @@
       </c>
       <c r="S753" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -65639,7 +65639,7 @@
       </c>
       <c r="S754" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -65728,7 +65728,7 @@
       </c>
       <c r="S755" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -65817,7 +65817,7 @@
       </c>
       <c r="S756" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -65906,7 +65906,7 @@
       </c>
       <c r="S757" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -65995,7 +65995,7 @@
       </c>
       <c r="S758" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -66084,7 +66084,7 @@
       </c>
       <c r="S759" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -66173,7 +66173,7 @@
       </c>
       <c r="S760" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -66262,7 +66262,7 @@
       </c>
       <c r="S761" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -66351,7 +66351,7 @@
       </c>
       <c r="S762" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -66436,7 +66436,7 @@
       </c>
       <c r="S763" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -66521,7 +66521,7 @@
       </c>
       <c r="S764" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -66606,7 +66606,7 @@
       </c>
       <c r="S765" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -66691,7 +66691,7 @@
       </c>
       <c r="S766" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -66776,7 +66776,7 @@
       </c>
       <c r="S767" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -66861,7 +66861,7 @@
       </c>
       <c r="S768" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -66946,7 +66946,7 @@
       </c>
       <c r="S769" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -67031,7 +67031,7 @@
       </c>
       <c r="S770" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -67116,7 +67116,7 @@
       </c>
       <c r="S771" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -67201,7 +67201,7 @@
       </c>
       <c r="S772" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -67286,7 +67286,7 @@
       </c>
       <c r="S773" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -67375,7 +67375,7 @@
       </c>
       <c r="S774" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -67464,7 +67464,7 @@
       </c>
       <c r="S775" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -67553,7 +67553,7 @@
       </c>
       <c r="S776" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -67642,7 +67642,7 @@
       </c>
       <c r="S777" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -67731,7 +67731,7 @@
       </c>
       <c r="S778" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -67820,7 +67820,7 @@
       </c>
       <c r="S779" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -67909,7 +67909,7 @@
       </c>
       <c r="S780" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -67998,7 +67998,7 @@
       </c>
       <c r="S781" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -68087,7 +68087,7 @@
       </c>
       <c r="S782" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -68176,7 +68176,7 @@
       </c>
       <c r="S783" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -68261,7 +68261,7 @@
       </c>
       <c r="S784" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -68346,7 +68346,7 @@
       </c>
       <c r="S785" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -68431,7 +68431,7 @@
       </c>
       <c r="S786" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -68516,7 +68516,7 @@
       </c>
       <c r="S787" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -68601,7 +68601,7 @@
       </c>
       <c r="S788" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -68686,7 +68686,7 @@
       </c>
       <c r="S789" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -68771,7 +68771,7 @@
       </c>
       <c r="S790" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -68856,7 +68856,7 @@
       </c>
       <c r="S791" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -68941,7 +68941,7 @@
       </c>
       <c r="S792" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -69026,7 +69026,7 @@
       </c>
       <c r="S793" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -69111,7 +69111,7 @@
       </c>
       <c r="S794" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -69200,7 +69200,7 @@
       </c>
       <c r="S795" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -69289,7 +69289,7 @@
       </c>
       <c r="S796" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -69378,7 +69378,7 @@
       </c>
       <c r="S797" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -69467,7 +69467,7 @@
       </c>
       <c r="S798" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -69556,7 +69556,7 @@
       </c>
       <c r="S799" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -69645,7 +69645,7 @@
       </c>
       <c r="S800" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -69734,7 +69734,7 @@
       </c>
       <c r="S801" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -69823,7 +69823,7 @@
       </c>
       <c r="S802" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -69912,7 +69912,7 @@
       </c>
       <c r="S803" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -70001,7 +70001,7 @@
       </c>
       <c r="S804" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -70086,7 +70086,7 @@
       </c>
       <c r="S805" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -70171,7 +70171,7 @@
       </c>
       <c r="S806" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -70256,7 +70256,7 @@
       </c>
       <c r="S807" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -70341,7 +70341,7 @@
       </c>
       <c r="S808" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -70426,7 +70426,7 @@
       </c>
       <c r="S809" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -70511,7 +70511,7 @@
       </c>
       <c r="S810" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -70596,7 +70596,7 @@
       </c>
       <c r="S811" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -70681,7 +70681,7 @@
       </c>
       <c r="S812" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -70766,7 +70766,7 @@
       </c>
       <c r="S813" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -70851,7 +70851,7 @@
       </c>
       <c r="S814" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -70936,7 +70936,7 @@
       </c>
       <c r="S815" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -71021,7 +71021,7 @@
       </c>
       <c r="S816" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -71106,7 +71106,7 @@
       </c>
       <c r="S817" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -71191,7 +71191,7 @@
       </c>
       <c r="S818" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -71276,7 +71276,7 @@
       </c>
       <c r="S819" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -71361,7 +71361,7 @@
       </c>
       <c r="S820" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -71446,7 +71446,7 @@
       </c>
       <c r="S821" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -71531,7 +71531,7 @@
       </c>
       <c r="S822" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -71616,7 +71616,7 @@
       </c>
       <c r="S823" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -71701,7 +71701,7 @@
       </c>
       <c r="S824" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -71786,7 +71786,7 @@
       </c>
       <c r="S825" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -71871,7 +71871,7 @@
       </c>
       <c r="S826" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -71960,7 +71960,7 @@
       </c>
       <c r="S827" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -72049,7 +72049,7 @@
       </c>
       <c r="S828" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -72138,7 +72138,7 @@
       </c>
       <c r="S829" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -72227,7 +72227,7 @@
       </c>
       <c r="S830" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -72316,7 +72316,7 @@
       </c>
       <c r="S831" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -72405,7 +72405,7 @@
       </c>
       <c r="S832" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -72494,7 +72494,7 @@
       </c>
       <c r="S833" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -72583,7 +72583,7 @@
       </c>
       <c r="S834" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -72672,7 +72672,7 @@
       </c>
       <c r="S835" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -72761,7 +72761,7 @@
       </c>
       <c r="S836" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -72850,7 +72850,7 @@
       </c>
       <c r="S837" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -72939,7 +72939,7 @@
       </c>
       <c r="S838" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -73028,7 +73028,7 @@
       </c>
       <c r="S839" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -73117,7 +73117,7 @@
       </c>
       <c r="S840" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -73206,7 +73206,7 @@
       </c>
       <c r="S841" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -73295,7 +73295,7 @@
       </c>
       <c r="S842" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -73384,7 +73384,7 @@
       </c>
       <c r="S843" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -73473,7 +73473,7 @@
       </c>
       <c r="S844" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -73562,7 +73562,7 @@
       </c>
       <c r="S845" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -73651,7 +73651,7 @@
       </c>
       <c r="S846" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -73736,7 +73736,7 @@
       </c>
       <c r="S847" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -73821,7 +73821,7 @@
       </c>
       <c r="S848" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -73906,7 +73906,7 @@
       </c>
       <c r="S849" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -73991,7 +73991,7 @@
       </c>
       <c r="S850" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -74076,7 +74076,7 @@
       </c>
       <c r="S851" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -74161,7 +74161,7 @@
       </c>
       <c r="S852" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -74246,7 +74246,7 @@
       </c>
       <c r="S853" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -74331,7 +74331,7 @@
       </c>
       <c r="S854" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -74416,7 +74416,7 @@
       </c>
       <c r="S855" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -74501,7 +74501,7 @@
       </c>
       <c r="S856" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -74586,7 +74586,7 @@
       </c>
       <c r="S857" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -74671,7 +74671,7 @@
       </c>
       <c r="S858" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -74756,7 +74756,7 @@
       </c>
       <c r="S859" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -74841,7 +74841,7 @@
       </c>
       <c r="S860" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -74926,7 +74926,7 @@
       </c>
       <c r="S861" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -75011,7 +75011,7 @@
       </c>
       <c r="S862" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -75096,7 +75096,7 @@
       </c>
       <c r="S863" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -75181,7 +75181,7 @@
       </c>
       <c r="S864" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -75266,7 +75266,7 @@
       </c>
       <c r="S865" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -75351,7 +75351,7 @@
       </c>
       <c r="S866" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -75436,7 +75436,7 @@
       </c>
       <c r="S867" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -75521,7 +75521,7 @@
       </c>
       <c r="S868" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -75610,7 +75610,7 @@
       </c>
       <c r="S869" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -75699,7 +75699,7 @@
       </c>
       <c r="S870" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -75788,7 +75788,7 @@
       </c>
       <c r="S871" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -75877,7 +75877,7 @@
       </c>
       <c r="S872" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -75966,7 +75966,7 @@
       </c>
       <c r="S873" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -76055,7 +76055,7 @@
       </c>
       <c r="S874" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -76144,7 +76144,7 @@
       </c>
       <c r="S875" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -76233,7 +76233,7 @@
       </c>
       <c r="S876" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -76322,7 +76322,7 @@
       </c>
       <c r="S877" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -76411,7 +76411,7 @@
       </c>
       <c r="S878" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -76500,7 +76500,7 @@
       </c>
       <c r="S879" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -76589,7 +76589,7 @@
       </c>
       <c r="S880" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -76678,7 +76678,7 @@
       </c>
       <c r="S881" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -76767,7 +76767,7 @@
       </c>
       <c r="S882" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -76856,7 +76856,7 @@
       </c>
       <c r="S883" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -76945,7 +76945,7 @@
       </c>
       <c r="S884" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -77034,7 +77034,7 @@
       </c>
       <c r="S885" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -77123,7 +77123,7 @@
       </c>
       <c r="S886" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -77212,7 +77212,7 @@
       </c>
       <c r="S887" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -77301,7 +77301,7 @@
       </c>
       <c r="S888" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -77433,7 +77433,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T17:10:08Z</t>
+          <t>2026-09-02T22:45:38Z</t>
         </is>
       </c>
     </row>
@@ -77513,7 +77513,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-09-02T17:10:08Z"}</t>
+          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-09-02T22:45:38Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_demanda_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12625,7 +12625,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -13936,7 +13936,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14446,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -15041,7 +15041,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15296,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16008,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -17161,7 +17161,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -17416,7 +17416,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -17501,7 +17501,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17586,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17671,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -17841,7 +17841,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -18011,7 +18011,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -18100,7 +18100,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -18367,7 +18367,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -18812,7 +18812,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -19326,7 +19326,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -19836,7 +19836,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -20176,7 +20176,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -20261,7 +20261,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -20686,7 +20686,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -20941,7 +20941,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -21026,7 +21026,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -21281,7 +21281,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -21536,7 +21536,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -21706,7 +21706,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -21795,7 +21795,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -21884,7 +21884,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -22062,7 +22062,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -22151,7 +22151,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -22240,7 +22240,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -22507,7 +22507,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22596,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -22685,7 +22685,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -22774,7 +22774,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -22952,7 +22952,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -23041,7 +23041,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -23130,7 +23130,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -23308,7 +23308,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -23397,7 +23397,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -23486,7 +23486,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -23575,7 +23575,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -23753,7 +23753,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24198,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -24287,7 +24287,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -24376,7 +24376,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -24461,7 +24461,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -24716,7 +24716,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -24886,7 +24886,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -24971,7 +24971,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25056,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -25226,7 +25226,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25396,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -25566,7 +25566,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -25736,7 +25736,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -25906,7 +25906,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -26076,7 +26076,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -26161,7 +26161,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -26335,7 +26335,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -26424,7 +26424,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -26602,7 +26602,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -26780,7 +26780,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -26869,7 +26869,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -26958,7 +26958,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -27225,7 +27225,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -27403,7 +27403,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -27492,7 +27492,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -27670,7 +27670,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -27759,7 +27759,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -27848,7 +27848,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -27937,7 +27937,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -28026,7 +28026,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -28196,7 +28196,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28281,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -28366,7 +28366,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -28451,7 +28451,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -28876,7 +28876,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28961,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -29046,7 +29046,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -29216,7 +29216,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -29301,7 +29301,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -29386,7 +29386,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -29471,7 +29471,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -29556,7 +29556,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -29641,7 +29641,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -29726,7 +29726,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -29811,7 +29811,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -29985,7 +29985,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -30341,7 +30341,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -30430,7 +30430,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30519,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -30608,7 +30608,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -31231,7 +31231,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -31498,7 +31498,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -31587,7 +31587,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -31676,7 +31676,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -31761,7 +31761,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -31846,7 +31846,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -31931,7 +31931,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -32101,7 +32101,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -32186,7 +32186,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -32271,7 +32271,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -32356,7 +32356,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -32441,7 +32441,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -32526,7 +32526,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -32611,7 +32611,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -32696,7 +32696,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -32781,7 +32781,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -32951,7 +32951,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -33036,7 +33036,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -33121,7 +33121,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -33291,7 +33291,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -33376,7 +33376,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -33461,7 +33461,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -33724,7 +33724,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -33813,7 +33813,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -33902,7 +33902,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -33991,7 +33991,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -34080,7 +34080,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -34169,7 +34169,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -34258,7 +34258,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -34347,7 +34347,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -34436,7 +34436,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -34525,7 +34525,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -34614,7 +34614,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -34703,7 +34703,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -34881,7 +34881,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -34970,7 +34970,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -35059,7 +35059,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -35148,7 +35148,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -35237,7 +35237,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -35326,7 +35326,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -35411,7 +35411,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -35496,7 +35496,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -35581,7 +35581,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -35666,7 +35666,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -35836,7 +35836,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -36006,7 +36006,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -36091,7 +36091,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -36176,7 +36176,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -36261,7 +36261,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -36350,7 +36350,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -36439,7 +36439,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -36617,7 +36617,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -36706,7 +36706,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -36795,7 +36795,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -36884,7 +36884,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -36973,7 +36973,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -37062,7 +37062,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -37151,7 +37151,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -37236,7 +37236,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -37321,7 +37321,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -37491,7 +37491,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -37576,7 +37576,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -37661,7 +37661,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -37746,7 +37746,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -37831,7 +37831,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -37916,7 +37916,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -38001,7 +38001,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -38086,7 +38086,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -38171,7 +38171,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -38256,7 +38256,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -38341,7 +38341,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -38426,7 +38426,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -38511,7 +38511,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -38596,7 +38596,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38681,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -38766,7 +38766,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -38851,7 +38851,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -38936,7 +38936,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -39021,7 +39021,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -39110,7 +39110,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -39199,7 +39199,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -39288,7 +39288,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -39377,7 +39377,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -39466,7 +39466,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -39644,7 +39644,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -39733,7 +39733,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -39822,7 +39822,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -39911,7 +39911,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -40000,7 +40000,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -40089,7 +40089,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -40178,7 +40178,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -40267,7 +40267,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -40356,7 +40356,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -40445,7 +40445,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -40534,7 +40534,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -40623,7 +40623,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -40712,7 +40712,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -40886,7 +40886,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -40971,7 +40971,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -41141,7 +41141,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -41226,7 +41226,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -41311,7 +41311,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -41396,7 +41396,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -41481,7 +41481,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -41566,7 +41566,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -41651,7 +41651,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -41736,7 +41736,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -41825,7 +41825,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -41914,7 +41914,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -42003,7 +42003,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -42092,7 +42092,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -42181,7 +42181,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -42270,7 +42270,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -42359,7 +42359,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -42448,7 +42448,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -42537,7 +42537,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -42626,7 +42626,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -42711,7 +42711,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -42796,7 +42796,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -42881,7 +42881,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -43051,7 +43051,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -43221,7 +43221,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -43306,7 +43306,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -43391,7 +43391,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -43476,7 +43476,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -43561,7 +43561,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -43646,7 +43646,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -43731,7 +43731,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -43816,7 +43816,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -43901,7 +43901,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -43986,7 +43986,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -44071,7 +44071,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -44156,7 +44156,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -44241,7 +44241,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -44326,7 +44326,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -44411,7 +44411,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -44496,7 +44496,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -44585,7 +44585,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -44674,7 +44674,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -44763,7 +44763,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -44852,7 +44852,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -44941,7 +44941,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -45030,7 +45030,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -45119,7 +45119,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -45208,7 +45208,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -45297,7 +45297,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -45386,7 +45386,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -45475,7 +45475,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -45564,7 +45564,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -45653,7 +45653,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -45742,7 +45742,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -45831,7 +45831,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -45920,7 +45920,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -46009,7 +46009,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -46098,7 +46098,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -46187,7 +46187,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -46276,7 +46276,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -46361,7 +46361,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -46446,7 +46446,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -46531,7 +46531,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -46616,7 +46616,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -46701,7 +46701,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -46786,7 +46786,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -46871,7 +46871,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -46956,7 +46956,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -47041,7 +47041,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -47126,7 +47126,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -47211,7 +47211,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -47300,7 +47300,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -47389,7 +47389,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -47478,7 +47478,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -47567,7 +47567,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -47656,7 +47656,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -47745,7 +47745,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -47834,7 +47834,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -47923,7 +47923,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -48012,7 +48012,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -48101,7 +48101,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -48186,7 +48186,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -48271,7 +48271,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -48356,7 +48356,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -48441,7 +48441,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -48526,7 +48526,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -48696,7 +48696,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -48781,7 +48781,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -48866,7 +48866,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -48951,7 +48951,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -49036,7 +49036,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -49125,7 +49125,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -49214,7 +49214,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -49303,7 +49303,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -49392,7 +49392,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -49481,7 +49481,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -49570,7 +49570,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -49659,7 +49659,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -49748,7 +49748,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -49837,7 +49837,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -49926,7 +49926,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -50011,7 +50011,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -50096,7 +50096,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -50181,7 +50181,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -50266,7 +50266,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -50436,7 +50436,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -50521,7 +50521,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -50606,7 +50606,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -50691,7 +50691,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -50776,7 +50776,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -50861,7 +50861,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -50946,7 +50946,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -51031,7 +51031,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -51116,7 +51116,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -51201,7 +51201,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -51286,7 +51286,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -51371,7 +51371,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -51456,7 +51456,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -51541,7 +51541,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -51626,7 +51626,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -51711,7 +51711,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -51796,7 +51796,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -51885,7 +51885,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -51974,7 +51974,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -52063,7 +52063,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -52152,7 +52152,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -52241,7 +52241,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -52330,7 +52330,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -52419,7 +52419,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -52508,7 +52508,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -52597,7 +52597,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -52686,7 +52686,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -52775,7 +52775,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -52864,7 +52864,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -52953,7 +52953,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -53042,7 +53042,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -53131,7 +53131,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -53220,7 +53220,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -53309,7 +53309,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -53398,7 +53398,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -53487,7 +53487,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -53576,7 +53576,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -53661,7 +53661,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -53746,7 +53746,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -53831,7 +53831,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -53916,7 +53916,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -54001,7 +54001,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -54086,7 +54086,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -54171,7 +54171,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -54256,7 +54256,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -54426,7 +54426,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -54511,7 +54511,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -54596,7 +54596,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -54681,7 +54681,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -54766,7 +54766,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -54851,7 +54851,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -54936,7 +54936,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -55021,7 +55021,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -55106,7 +55106,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -55191,7 +55191,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -55276,7 +55276,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -55361,7 +55361,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -55446,7 +55446,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -55531,7 +55531,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -55616,7 +55616,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -55701,7 +55701,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -55786,7 +55786,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -55871,7 +55871,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -55956,7 +55956,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -56041,7 +56041,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -56126,7 +56126,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -56211,7 +56211,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -56296,7 +56296,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -56381,7 +56381,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -56466,7 +56466,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -56551,7 +56551,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -56636,7 +56636,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -56721,7 +56721,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -56806,7 +56806,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -56891,7 +56891,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -56976,7 +56976,7 @@
       </c>
       <c r="S655" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -57061,7 +57061,7 @@
       </c>
       <c r="S656" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -57146,7 +57146,7 @@
       </c>
       <c r="S657" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -57231,7 +57231,7 @@
       </c>
       <c r="S658" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -57316,7 +57316,7 @@
       </c>
       <c r="S659" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -57401,7 +57401,7 @@
       </c>
       <c r="S660" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -57486,7 +57486,7 @@
       </c>
       <c r="S661" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -57571,7 +57571,7 @@
       </c>
       <c r="S662" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -57656,7 +57656,7 @@
       </c>
       <c r="S663" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -57741,7 +57741,7 @@
       </c>
       <c r="S664" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -57826,7 +57826,7 @@
       </c>
       <c r="S665" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -57911,7 +57911,7 @@
       </c>
       <c r="S666" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -57996,7 +57996,7 @@
       </c>
       <c r="S667" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -58081,7 +58081,7 @@
       </c>
       <c r="S668" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -58166,7 +58166,7 @@
       </c>
       <c r="S669" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -58251,7 +58251,7 @@
       </c>
       <c r="S670" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -58340,7 +58340,7 @@
       </c>
       <c r="S671" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -58429,7 +58429,7 @@
       </c>
       <c r="S672" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -58518,7 +58518,7 @@
       </c>
       <c r="S673" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -58607,7 +58607,7 @@
       </c>
       <c r="S674" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -58696,7 +58696,7 @@
       </c>
       <c r="S675" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -58785,7 +58785,7 @@
       </c>
       <c r="S676" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -58874,7 +58874,7 @@
       </c>
       <c r="S677" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -58963,7 +58963,7 @@
       </c>
       <c r="S678" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -59052,7 +59052,7 @@
       </c>
       <c r="S679" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -59141,7 +59141,7 @@
       </c>
       <c r="S680" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -59230,7 +59230,7 @@
       </c>
       <c r="S681" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -59319,7 +59319,7 @@
       </c>
       <c r="S682" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -59408,7 +59408,7 @@
       </c>
       <c r="S683" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -59497,7 +59497,7 @@
       </c>
       <c r="S684" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -59586,7 +59586,7 @@
       </c>
       <c r="S685" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -59675,7 +59675,7 @@
       </c>
       <c r="S686" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -59764,7 +59764,7 @@
       </c>
       <c r="S687" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -59853,7 +59853,7 @@
       </c>
       <c r="S688" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -59942,7 +59942,7 @@
       </c>
       <c r="S689" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -60031,7 +60031,7 @@
       </c>
       <c r="S690" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -60120,7 +60120,7 @@
       </c>
       <c r="S691" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -60209,7 +60209,7 @@
       </c>
       <c r="S692" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -60298,7 +60298,7 @@
       </c>
       <c r="S693" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -60387,7 +60387,7 @@
       </c>
       <c r="S694" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -60476,7 +60476,7 @@
       </c>
       <c r="S695" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -60565,7 +60565,7 @@
       </c>
       <c r="S696" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -60654,7 +60654,7 @@
       </c>
       <c r="S697" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -60743,7 +60743,7 @@
       </c>
       <c r="S698" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -60832,7 +60832,7 @@
       </c>
       <c r="S699" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -60921,7 +60921,7 @@
       </c>
       <c r="S700" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -61010,7 +61010,7 @@
       </c>
       <c r="S701" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -61099,7 +61099,7 @@
       </c>
       <c r="S702" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -61188,7 +61188,7 @@
       </c>
       <c r="S703" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -61277,7 +61277,7 @@
       </c>
       <c r="S704" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -61366,7 +61366,7 @@
       </c>
       <c r="S705" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -61455,7 +61455,7 @@
       </c>
       <c r="S706" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -61544,7 +61544,7 @@
       </c>
       <c r="S707" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -61633,7 +61633,7 @@
       </c>
       <c r="S708" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -61722,7 +61722,7 @@
       </c>
       <c r="S709" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -61811,7 +61811,7 @@
       </c>
       <c r="S710" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -61900,7 +61900,7 @@
       </c>
       <c r="S711" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -61989,7 +61989,7 @@
       </c>
       <c r="S712" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -62078,7 +62078,7 @@
       </c>
       <c r="S713" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -62167,7 +62167,7 @@
       </c>
       <c r="S714" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -62256,7 +62256,7 @@
       </c>
       <c r="S715" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -62345,7 +62345,7 @@
       </c>
       <c r="S716" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -62434,7 +62434,7 @@
       </c>
       <c r="S717" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -62523,7 +62523,7 @@
       </c>
       <c r="S718" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -62612,7 +62612,7 @@
       </c>
       <c r="S719" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -62701,7 +62701,7 @@
       </c>
       <c r="S720" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -62786,7 +62786,7 @@
       </c>
       <c r="S721" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -62871,7 +62871,7 @@
       </c>
       <c r="S722" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -62956,7 +62956,7 @@
       </c>
       <c r="S723" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -63041,7 +63041,7 @@
       </c>
       <c r="S724" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -63126,7 +63126,7 @@
       </c>
       <c r="S725" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -63211,7 +63211,7 @@
       </c>
       <c r="S726" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -63296,7 +63296,7 @@
       </c>
       <c r="S727" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -63381,7 +63381,7 @@
       </c>
       <c r="S728" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -63466,7 +63466,7 @@
       </c>
       <c r="S729" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -63551,7 +63551,7 @@
       </c>
       <c r="S730" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -63636,7 +63636,7 @@
       </c>
       <c r="S731" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -63721,7 +63721,7 @@
       </c>
       <c r="S732" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -63806,7 +63806,7 @@
       </c>
       <c r="S733" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -63891,7 +63891,7 @@
       </c>
       <c r="S734" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -63976,7 +63976,7 @@
       </c>
       <c r="S735" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -64061,7 +64061,7 @@
       </c>
       <c r="S736" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -64146,7 +64146,7 @@
       </c>
       <c r="S737" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -64231,7 +64231,7 @@
       </c>
       <c r="S738" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -64316,7 +64316,7 @@
       </c>
       <c r="S739" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -64401,7 +64401,7 @@
       </c>
       <c r="S740" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -64486,7 +64486,7 @@
       </c>
       <c r="S741" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -64571,7 +64571,7 @@
       </c>
       <c r="S742" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -64660,7 +64660,7 @@
       </c>
       <c r="S743" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -64749,7 +64749,7 @@
       </c>
       <c r="S744" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -64838,7 +64838,7 @@
       </c>
       <c r="S745" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -64927,7 +64927,7 @@
       </c>
       <c r="S746" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -65016,7 +65016,7 @@
       </c>
       <c r="S747" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -65105,7 +65105,7 @@
       </c>
       <c r="S748" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -65194,7 +65194,7 @@
       </c>
       <c r="S749" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -65283,7 +65283,7 @@
       </c>
       <c r="S750" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -65372,7 +65372,7 @@
       </c>
       <c r="S751" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -65461,7 +65461,7 @@
       </c>
       <c r="S752" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -65550,7 +65550,7 @@
       </c>
       <c r="S753" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -65639,7 +65639,7 @@
       </c>
       <c r="S754" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -65728,7 +65728,7 @@
       </c>
       <c r="S755" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -65817,7 +65817,7 @@
       </c>
       <c r="S756" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -65906,7 +65906,7 @@
       </c>
       <c r="S757" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -65995,7 +65995,7 @@
       </c>
       <c r="S758" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -66084,7 +66084,7 @@
       </c>
       <c r="S759" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -66173,7 +66173,7 @@
       </c>
       <c r="S760" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -66262,7 +66262,7 @@
       </c>
       <c r="S761" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -66351,7 +66351,7 @@
       </c>
       <c r="S762" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -66436,7 +66436,7 @@
       </c>
       <c r="S763" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -66521,7 +66521,7 @@
       </c>
       <c r="S764" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -66606,7 +66606,7 @@
       </c>
       <c r="S765" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -66691,7 +66691,7 @@
       </c>
       <c r="S766" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -66776,7 +66776,7 @@
       </c>
       <c r="S767" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -66861,7 +66861,7 @@
       </c>
       <c r="S768" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -66946,7 +66946,7 @@
       </c>
       <c r="S769" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -67031,7 +67031,7 @@
       </c>
       <c r="S770" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -67116,7 +67116,7 @@
       </c>
       <c r="S771" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -67201,7 +67201,7 @@
       </c>
       <c r="S772" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -67286,7 +67286,7 @@
       </c>
       <c r="S773" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -67375,7 +67375,7 @@
       </c>
       <c r="S774" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -67464,7 +67464,7 @@
       </c>
       <c r="S775" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -67553,7 +67553,7 @@
       </c>
       <c r="S776" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -67642,7 +67642,7 @@
       </c>
       <c r="S777" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -67731,7 +67731,7 @@
       </c>
       <c r="S778" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -67820,7 +67820,7 @@
       </c>
       <c r="S779" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -67909,7 +67909,7 @@
       </c>
       <c r="S780" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -67998,7 +67998,7 @@
       </c>
       <c r="S781" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -68087,7 +68087,7 @@
       </c>
       <c r="S782" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -68176,7 +68176,7 @@
       </c>
       <c r="S783" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -68261,7 +68261,7 @@
       </c>
       <c r="S784" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -68346,7 +68346,7 @@
       </c>
       <c r="S785" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -68431,7 +68431,7 @@
       </c>
       <c r="S786" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -68516,7 +68516,7 @@
       </c>
       <c r="S787" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -68601,7 +68601,7 @@
       </c>
       <c r="S788" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -68686,7 +68686,7 @@
       </c>
       <c r="S789" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -68771,7 +68771,7 @@
       </c>
       <c r="S790" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -68856,7 +68856,7 @@
       </c>
       <c r="S791" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -68941,7 +68941,7 @@
       </c>
       <c r="S792" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -69026,7 +69026,7 @@
       </c>
       <c r="S793" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -69111,7 +69111,7 @@
       </c>
       <c r="S794" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -69200,7 +69200,7 @@
       </c>
       <c r="S795" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -69289,7 +69289,7 @@
       </c>
       <c r="S796" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -69378,7 +69378,7 @@
       </c>
       <c r="S797" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -69467,7 +69467,7 @@
       </c>
       <c r="S798" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -69556,7 +69556,7 @@
       </c>
       <c r="S799" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -69645,7 +69645,7 @@
       </c>
       <c r="S800" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -69734,7 +69734,7 @@
       </c>
       <c r="S801" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -69823,7 +69823,7 @@
       </c>
       <c r="S802" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -69912,7 +69912,7 @@
       </c>
       <c r="S803" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -70001,7 +70001,7 @@
       </c>
       <c r="S804" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -70086,7 +70086,7 @@
       </c>
       <c r="S805" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -70171,7 +70171,7 @@
       </c>
       <c r="S806" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -70256,7 +70256,7 @@
       </c>
       <c r="S807" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -70341,7 +70341,7 @@
       </c>
       <c r="S808" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -70426,7 +70426,7 @@
       </c>
       <c r="S809" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -70511,7 +70511,7 @@
       </c>
       <c r="S810" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -70596,7 +70596,7 @@
       </c>
       <c r="S811" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -70681,7 +70681,7 @@
       </c>
       <c r="S812" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -70766,7 +70766,7 @@
       </c>
       <c r="S813" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -70851,7 +70851,7 @@
       </c>
       <c r="S814" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -70936,7 +70936,7 @@
       </c>
       <c r="S815" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -71021,7 +71021,7 @@
       </c>
       <c r="S816" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -71106,7 +71106,7 @@
       </c>
       <c r="S817" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -71191,7 +71191,7 @@
       </c>
       <c r="S818" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -71276,7 +71276,7 @@
       </c>
       <c r="S819" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -71361,7 +71361,7 @@
       </c>
       <c r="S820" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -71446,7 +71446,7 @@
       </c>
       <c r="S821" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -71531,7 +71531,7 @@
       </c>
       <c r="S822" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -71616,7 +71616,7 @@
       </c>
       <c r="S823" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -71701,7 +71701,7 @@
       </c>
       <c r="S824" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -71786,7 +71786,7 @@
       </c>
       <c r="S825" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -71871,7 +71871,7 @@
       </c>
       <c r="S826" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -71960,7 +71960,7 @@
       </c>
       <c r="S827" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -72049,7 +72049,7 @@
       </c>
       <c r="S828" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -72138,7 +72138,7 @@
       </c>
       <c r="S829" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -72227,7 +72227,7 @@
       </c>
       <c r="S830" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -72316,7 +72316,7 @@
       </c>
       <c r="S831" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -72405,7 +72405,7 @@
       </c>
       <c r="S832" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -72494,7 +72494,7 @@
       </c>
       <c r="S833" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -72583,7 +72583,7 @@
       </c>
       <c r="S834" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -72672,7 +72672,7 @@
       </c>
       <c r="S835" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -72761,7 +72761,7 @@
       </c>
       <c r="S836" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -72850,7 +72850,7 @@
       </c>
       <c r="S837" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -72939,7 +72939,7 @@
       </c>
       <c r="S838" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -73028,7 +73028,7 @@
       </c>
       <c r="S839" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -73117,7 +73117,7 @@
       </c>
       <c r="S840" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -73206,7 +73206,7 @@
       </c>
       <c r="S841" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -73295,7 +73295,7 @@
       </c>
       <c r="S842" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -73384,7 +73384,7 @@
       </c>
       <c r="S843" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -73473,7 +73473,7 @@
       </c>
       <c r="S844" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -73562,7 +73562,7 @@
       </c>
       <c r="S845" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -73651,7 +73651,7 @@
       </c>
       <c r="S846" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -73736,7 +73736,7 @@
       </c>
       <c r="S847" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -73821,7 +73821,7 @@
       </c>
       <c r="S848" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -73906,7 +73906,7 @@
       </c>
       <c r="S849" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -73991,7 +73991,7 @@
       </c>
       <c r="S850" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -74076,7 +74076,7 @@
       </c>
       <c r="S851" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -74161,7 +74161,7 @@
       </c>
       <c r="S852" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -74246,7 +74246,7 @@
       </c>
       <c r="S853" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -74331,7 +74331,7 @@
       </c>
       <c r="S854" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -74416,7 +74416,7 @@
       </c>
       <c r="S855" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -74501,7 +74501,7 @@
       </c>
       <c r="S856" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -74586,7 +74586,7 @@
       </c>
       <c r="S857" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -74671,7 +74671,7 @@
       </c>
       <c r="S858" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -74756,7 +74756,7 @@
       </c>
       <c r="S859" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -74841,7 +74841,7 @@
       </c>
       <c r="S860" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -74926,7 +74926,7 @@
       </c>
       <c r="S861" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -75011,7 +75011,7 @@
       </c>
       <c r="S862" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -75096,7 +75096,7 @@
       </c>
       <c r="S863" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -75181,7 +75181,7 @@
       </c>
       <c r="S864" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -75266,7 +75266,7 @@
       </c>
       <c r="S865" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -75351,7 +75351,7 @@
       </c>
       <c r="S866" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -75436,7 +75436,7 @@
       </c>
       <c r="S867" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -75521,7 +75521,7 @@
       </c>
       <c r="S868" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -75610,7 +75610,7 @@
       </c>
       <c r="S869" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -75699,7 +75699,7 @@
       </c>
       <c r="S870" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -75788,7 +75788,7 @@
       </c>
       <c r="S871" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -75877,7 +75877,7 @@
       </c>
       <c r="S872" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -75966,7 +75966,7 @@
       </c>
       <c r="S873" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -76055,7 +76055,7 @@
       </c>
       <c r="S874" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -76144,7 +76144,7 @@
       </c>
       <c r="S875" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -76233,7 +76233,7 @@
       </c>
       <c r="S876" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -76322,7 +76322,7 @@
       </c>
       <c r="S877" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -76411,7 +76411,7 @@
       </c>
       <c r="S878" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -76500,7 +76500,7 @@
       </c>
       <c r="S879" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -76589,7 +76589,7 @@
       </c>
       <c r="S880" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -76678,7 +76678,7 @@
       </c>
       <c r="S881" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -76767,7 +76767,7 @@
       </c>
       <c r="S882" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -76856,7 +76856,7 @@
       </c>
       <c r="S883" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -76945,7 +76945,7 @@
       </c>
       <c r="S884" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -77034,7 +77034,7 @@
       </c>
       <c r="S885" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -77123,7 +77123,7 @@
       </c>
       <c r="S886" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -77212,7 +77212,7 @@
       </c>
       <c r="S887" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -77301,7 +77301,7 @@
       </c>
       <c r="S888" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -77433,7 +77433,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08T22:51:30Z</t>
+          <t>2026-09-09T22:40:34Z</t>
         </is>
       </c>
     </row>
@@ -77513,7 +77513,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-09-08T22:51:30Z"}</t>
+          <t>{"dataset_id": "bcv_pib_demanda_anual", "title": "Producto interno bruto por componentes de demanda", "table": "Componentes del PIB", "source_file": "7_1_7_anual.xls", "base": "Escala monetaria vigente desde 2018", "price_type": "Precios corrientes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Enfoque del ingreso", "component": "Excedente de explotación, bruto", "value": 1094922967.5, "unit": "Bolívares", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_7_anual.xls", "fetched_at": "2026-09-09T22:40:34Z"}</t>
         </is>
       </c>
     </row>
